--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -17263,25 +17263,25 @@
         </is>
       </c>
       <c r="K161" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L161" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M161" s="1" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N161" s="1" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="O161" s="1" t="n">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="P161" s="1" t="n">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="Q161" s="1" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R161" s="1" t="n">
         <v>6</v>
@@ -19198,7 +19198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25797,70 +25797,70 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
+          <t>{n}연타!</t>
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>삭-제!! 회전회오리이이!!</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>핵꿀밤!</t>
+          <t>총 {n}연타!</t>
         </is>
       </c>
       <c r="D294" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
@@ -25870,12 +25870,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>{n}회전… 양호!</t>
+          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
         </is>
       </c>
       <c r="D295" s="2" t="n">
@@ -25883,7 +25883,7 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25893,16 +25893,16 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>양호띠!! (엄지 척)</t>
+          <t>삭-제!! 회전회오리이이!!</t>
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -25916,12 +25916,12 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>스읍- Miss.</t>
+          <t>핵꿀밤!</t>
         </is>
       </c>
       <c r="D297" s="2" t="n">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -25939,20 +25939,20 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>쌉전드…</t>
+          <t>{n}회전… 양호!</t>
         </is>
       </c>
       <c r="D298" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25962,20 +25962,20 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>여기 어디야? 천국이네~</t>
+          <t>양호띠!! (엄지 척)</t>
         </is>
       </c>
       <c r="D299" s="2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -25985,20 +25985,20 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>컷.</t>
+          <t>스읍- Miss.</t>
         </is>
       </c>
       <c r="D300" s="2" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -26008,18 +26008,87 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
+          <t>c7</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>쌉전드…</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>#f2c94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>c8</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>여기 어디야? 천국이네~</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>c9</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>컷.</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
           <t>c10</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
+      <c r="C304" s="2" t="inlineStr">
         <is>
           <t>(치즈분수 참사 2탄)</t>
         </is>
       </c>
-      <c r="D301" s="2" t="n">
+      <c r="D304" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="E301" s="2" t="inlineStr">
+      <c r="E304" s="2" t="inlineStr">
         <is>
           <t>#9aa0a6</t>
         </is>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -18310,17 +18310,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>로열 티타임</t>
+          <t>여왕 폐하의 근위대</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>UltTableFlip</t>
+          <t>UltRoyalGuard</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>물건을 식탁에 모아 티타임 → 밥상 뒤집기</t>
+          <t>근위병 쥐들이 줄지어 행진하며 물건을 밀어붙임 → 여왕은 마차에서 손 흔들기 → 받들어 총 충격파</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -18338,12 +18338,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>호호호~ 차 한잔… 하면서!!</t>
+          <t>근위대, 앞으로 가!</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>우아한 밥상 뒤집기</t>
+          <t>줄 서세요 (강제)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>tableflip</t>
+          <t>royalguard</t>
         </is>
       </c>
     </row>
@@ -18571,17 +18571,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>꿈과 치즈의 풍선 퍼레이드</t>
+          <t>쥐랜드 성 대개장</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UltBalloonParade</t>
+          <t>UltRatlandLawsuit</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>물건·사람에 하트 풍선을 달아 둥실 퍼레이드 → 풍선이 펑펑 터지며 와르르</t>
+          <t>쥐랜드 성이 솟아오름 → 변호사 쥐들이 몰려나와 물건마다 압류 딱지 → 성 대폭발</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -18599,12 +18599,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>다 같이 퍼레이드~! 사진 찍어 주세요!</t>
+          <t>하하! 쥐랜드에 온 걸 환영해!</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>기념품 풍선은 개당 5만 원</t>
+          <t>저작권은 소중하니까요</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>balloonparade</t>
+          <t>lawsuit</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19304,7 +19304,7 @@
       <c r="D4" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -19323,7 +19323,7 @@
       <c r="D5" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -19342,7 +19342,7 @@
       <c r="D6" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -19361,7 +19361,7 @@
       <c r="D7" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -19426,7 +19426,7 @@
       <c r="D10" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -19491,7 +19491,7 @@
       <c r="D13" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -19510,7 +19510,7 @@
       <c r="D14" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -19529,7 +19529,7 @@
       <c r="D15" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -19548,7 +19548,7 @@
       <c r="D16" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -19590,7 +19590,7 @@
       <c r="D18" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -19632,7 +19632,7 @@
       <c r="D20" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -19674,7 +19674,7 @@
       <c r="D22" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -19716,7 +19716,7 @@
       <c r="D24" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -19735,7 +19735,7 @@
       <c r="D25" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -19777,7 +19777,7 @@
       <c r="D27" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -19796,7 +19796,7 @@
       <c r="D28" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -19861,7 +19861,7 @@
       <c r="D31" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -19880,7 +19880,7 @@
       <c r="D32" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -19991,7 +19991,7 @@
       <c r="D37" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -20033,7 +20033,7 @@
       <c r="D39" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -20144,7 +20144,7 @@
       <c r="D44" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -20186,7 +20186,7 @@
       <c r="D46" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -20205,7 +20205,7 @@
       <c r="D47" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -20293,7 +20293,7 @@
       <c r="D51" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -20358,7 +20358,7 @@
       <c r="D54" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -20607,7 +20607,7 @@
       <c r="D65" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -20902,7 +20902,7 @@
       <c r="D78" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -20944,7 +20944,7 @@
       <c r="D80" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -20971,47 +20971,47 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>30015</v>
+        <v>30014</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>(어디선가 킥킥 소리가 들린다…)</t>
+          <t>딸꾹!</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffd0d8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>30015</v>
+        <v>30014</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>킥킥킥… 쏜다!!</t>
+          <t>끅!</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>#9dbb8f</t>
+          <t>#ffd0d8</t>
         </is>
       </c>
     </row>
@@ -21021,12 +21021,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>(화살은 무한입니다. 킥킥)</t>
+          <t>(어디선가 킥킥 소리가 들린다…)</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
@@ -21044,20 +21044,20 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>(역병은 친환경 퇴비입니다)</t>
+          <t>킥킥킥… 쏜다!!</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#9dbb8f</t>
         </is>
       </c>
     </row>
@@ -21067,35 +21067,35 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>킥킥</t>
+          <t>(화살은 무한입니다. 킥킥)</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>#9dbb8f</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>30016</v>
+        <v>30015</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>꼬리가… 엉켰다?!</t>
+          <t>(역병은 친환경 퇴비입니다)</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
@@ -21109,24 +21109,24 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>30016</v>
+        <v>30015</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>※ 실제로 존재하는 현상입니다</t>
+          <t>킥킥</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9dbb8f</t>
         </is>
       </c>
     </row>
@@ -21136,12 +21136,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>(아무도 못 풀어요)</t>
+          <t>꼬리가… 엉켰다?!</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21159,18 +21159,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>(점점 더 엉킨다)</t>
+          <t>※ 실제로 존재하는 현상입니다</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -21178,39 +21182,39 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>풀렸다!!</t>
+          <t>(아무도 못 풀어요)</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>30017</v>
+        <v>30016</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>호호호~ 차 한잔 하렴~</t>
+          <t>(점점 더 엉킨다)</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -21220,20 +21224,20 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>30017</v>
+        <v>30016</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>(홀짝)</t>
+          <t>풀렸다!!</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -21247,16 +21251,16 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>(°□°) 밥상 뒤엎기!!</t>
+          <t>근위대, 집합!</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -21270,22 +21274,18 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>…호호. 한 잔 더 하렴~?</t>
+          <t>하나! 둘! 하나! 둘!</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>#fff3bf</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -21293,20 +21293,20 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>(°□°) 밥상 또 뒤엎기!!!</t>
+          <t>(근위병은 웃지 않는다)</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -21316,20 +21316,20 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>홀짝~</t>
+          <t>길을 비켜라~ 여왕 폐하 납신다!</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21339,66 +21339,66 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>홀짝… (부들부들)</t>
+          <t>호호호~ 손 흔들어 드리렴~</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>30018</v>
+        <v>30017</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>장전 완료! (나를)</t>
+          <t>착-! 받들어 총!</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>30018</v>
+        <v>30017</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>(안전장치 없음)</t>
+          <t>(물건들이 정렬당했다)</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -21408,12 +21408,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>한 번 더!!</t>
+          <t>장전 완료! (나를)</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -21421,7 +21421,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -21431,20 +21431,20 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>발할라!!</t>
+          <t>(안전장치 없음)</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -21454,16 +21454,16 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>우라아아아!!</t>
+          <t>한 번 더!!</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -21477,16 +21477,16 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>오딘이시여!!</t>
+          <t>발할라!!</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -21500,16 +21500,16 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>스콜!!! 발할라로!!</t>
+          <t>우라아아아!!</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -21519,20 +21519,20 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>30019</v>
+        <v>30018</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>변신!! 치키치키치키…</t>
+          <t>오딘이시여!!</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -21542,16 +21542,16 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>30019</v>
+        <v>30018</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>…자동차?</t>
+          <t>스콜!!! 발할라로!!</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
@@ -21569,12 +21569,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>(운전면허 없음)</t>
+          <t>변신!! 치키치키치키…</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21592,16 +21592,16 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>(과속 단속 카메라: 찰칵)</t>
+          <t>…자동차?</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -21615,12 +21615,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>(분해됨)</t>
+          <t>(운전면허 없음)</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -21638,20 +21638,20 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>치킹!</t>
+          <t>(과속 단속 카메라: 찰칵)</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21661,20 +21661,20 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>철컥!</t>
+          <t>(분해됨)</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21684,12 +21684,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>위잉!</t>
+          <t>치킹!</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
@@ -21707,16 +21707,16 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>철컥!</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -21730,66 +21730,66 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>빵빵!</t>
+          <t>위잉!</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>30020</v>
+        <v>30019</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>우주를… 재부팅한다.</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>30020</v>
+        <v>30019</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>(응답 없음) (응답 없음) (응답 없음)</t>
+          <t>빵빵!</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -21799,12 +21799,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>[강제 종료] 클릭!</t>
+          <t>우주를… 재부팅한다.</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
@@ -21812,22 +21812,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>(건전지 충전 중… 1.5V)</t>
+          <t>(응답 없음) (응답 없음) (응답 없음)</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -21835,164 +21835,164 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>찌이이이이릿!!!</t>
+          <t>[강제 종료] 클릭!</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>(전압 초과… 9V… 220V…)</t>
+          <t>우주.exe</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>#f2b8b0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>(건전지는 분리수거 해주세요)</t>
+          <t>우주.exe 가 응답하지 않습니다.</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#4b4540</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>찌릿!</t>
+          <t>(치즈가 너무 많이 부서짐)</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#4b4540</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>지지직!</t>
+          <t>기다리기</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#4b4540</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>(뼈가 보임)</t>
+          <t>강제 종료</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#4b4540</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>30021</v>
+        <v>30020</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>…(지지직)</t>
+          <t>!</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
@@ -22011,21 +22011,21 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>★ 꿈과 치즈의 나라로~ ★</t>
+          <t>(건전지 충전 중… 1.5V)</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
@@ -22034,21 +22034,21 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>(풍선 하나 5만 원)</t>
+          <t>찌이이이이릿!!!</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>#f2b8b0</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
@@ -22057,21 +22057,21 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>★ 퍼레이드는 한 바퀴 더~ ★</t>
+          <t>(전압 초과… 9V… 220V…)</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2b8b0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
@@ -22080,21 +22080,21 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>펑! 펑! 펑!</t>
+          <t>(건전지는 분리수거 해주세요)</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>#f2b8b0</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>30022</v>
+        <v>30021</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>펑!</t>
+          <t>찌릿!</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
@@ -22111,95 +22111,95 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>30023</v>
+        <v>30021</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>만세! 만만세!</t>
+          <t>지지직!</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>30023</v>
+        <v>30021</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>(불꽃놀이 안전 수칙: 무시)</t>
+          <t>(뼈가 보임)</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>30023</v>
+        <v>30021</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>(옆으로 쏘면 안 됩니다)</t>
+          <t>…(지지직)</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>30023</v>
+        <v>30022</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>만만만세!!!</t>
+          <t>하하! 꿈과 치즈의 나라로~!</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -22209,85 +22209,85 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>30023</v>
+        <v>30022</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>앗 뜨거!</t>
+          <t>어어어어…????</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>짐의 피라미드를 받들라!</t>
+          <t>(쥐랜드 법무팀 출동)</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>※ 다단계 아닙니다 (진짜로)</t>
+          <t>압류</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>치즈는 전부 꼭대기로~</t>
+          <t>저작권 침해입니다.</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
@@ -22301,131 +22301,131 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>피라미드… 팽이!!</t>
+          <t>이 물건도… 저것도… 전부 압류!</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>(짐도 멈추는 법을 모른다)</t>
+          <t>하하! …하?</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>(어지러워…)</t>
+          <t>(쥐랜드 성 철거 완료)</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>30024</v>
+        <v>30022</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>상납!</t>
+          <t>펑!</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>30024</v>
+        <v>30023</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>짐에게 바쳐라!</t>
+          <t>만세! 만만세!</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>30025</v>
+        <v>30023</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>전설의 검을 뽑는 자, 왕이 되리라…</t>
+          <t>(불꽃놀이 안전 수칙: 무시)</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
@@ -22433,22 +22433,22 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>30025</v>
+        <v>30023</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>…바위까지 딸려 나왔다.</t>
+          <t>(옆으로 쏘면 안 됩니다)</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -22462,16 +22462,16 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>30025</v>
+        <v>30023</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>그냥 이걸로 친다!!</t>
+          <t>만만만세!!!</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
@@ -22485,39 +22485,39 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>30025</v>
+        <v>30023</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>(멈추는 법은 안 배웠다)</t>
+          <t>앗 뜨거!</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>(이제야 진짜 검)</t>
+          <t>짐의 피라미드를 받들라!</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -22525,183 +22525,183 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>끄응…</t>
+          <t>※ 다단계 아닙니다 (진짜로)</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>끄으응…!</t>
+          <t>치즈는 전부 꼭대기로~</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>끄으으으응!!!</t>
+          <t>피라미드… 팽이!!</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>30026</v>
+        <v>30024</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>(램프를 문지른다… 쓱쓱)</t>
+          <t>(짐도 멈추는 법을 모른다)</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>30026</v>
+        <v>30024</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>소원을 말해 보거라~!!</t>
+          <t>(어지러워…)</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>#cdb4db</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>30026</v>
+        <v>30024</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>소원 1번: 물건 크게 해줘!</t>
+          <t>상납!</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>#cdb4db</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>30026</v>
+        <v>30024</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>소원 2번: 더 많이!!</t>
+          <t>짐에게 바쳐라!</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>30026</v>
+        <v>30025</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>소원 3번: …다 없어져라?</t>
+          <t>전설의 검을 뽑는 자, 왕이 되리라…</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
@@ -22709,118 +22709,118 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>30026</v>
+        <v>30025</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>(지니가 곡해함)</t>
+          <t>…바위까지 딸려 나왔다.</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>30026</v>
+        <v>30025</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>펑!</t>
+          <t>그냥 이걸로 친다!!</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>30027</v>
+        <v>30025</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>표본 채집 개시. 삐리.</t>
+          <t>(멈추는 법은 안 배웠다)</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>30027</v>
+        <v>30025</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>표본 부족. 더 채집한다. 삐리.</t>
+          <t>(이제야 진짜 검)</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>30027</v>
+        <v>30025</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>검사 완료. 반납합니다.</t>
+          <t>끄응…</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -22830,43 +22830,43 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>30027</v>
+        <v>30025</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>앗, 나는 빼줘!!</t>
+          <t>끄으응…!</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>30028</v>
+        <v>30025</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>● LIVE · 흐에~ 방송 중~</t>
+          <t>끄으으으응!!!</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -22876,16 +22876,16 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>(아 진짜요…?)</t>
+          <t>(램프를 문지른다… 쓱쓱)</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
@@ -22893,26 +22893,26 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>쥐커드 제노사이드!!!</t>
+          <t>소원을 말해 보거라~!!</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
@@ -22922,112 +22922,112 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>쥐커드 리마스터!!!!</t>
+          <t>소원 1번: 물건 크게 해줘!</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#cdb4db</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>★ 치즈 {n}개 후원!</t>
+          <t>소원 2번: 더 많이!!</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>★ 큰손 햄찌님 치즈 {n}개 후원!</t>
+          <t>소원 3번: …다 없어져라?</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>"쥐커드 리마스터 해줘!!!"</t>
+          <t>(지니가 곡해함)</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>30028</v>
+        <v>30026</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>"쥐커드 해주세요!!"</t>
+          <t>펑!</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
@@ -23037,43 +23037,43 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>"이이잉~~ 쥐커드!!"</t>
+          <t>표본 채집 개시. 삐리.</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>"믿고 있었다구!! 쥐커드!!"</t>
+          <t>표본 부족. 더 채집한다. 삐리.</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -23083,20 +23083,20 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>"앵콜!! 앵콜!!"</t>
+          <t>검사 완료. 반납합니다.</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
@@ -23106,24 +23106,24 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>"리마스터 가즈아!!"</t>
+          <t>앗, 나는 빼줘!!</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23133,16 +23133,16 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>"효과음 입으로 해주세요"</t>
+          <t>● LIVE · 흐에~ 방송 중~</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
@@ -23156,20 +23156,20 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>"엄마가 쥐커드 보래요"</t>
+          <t>(아 진짜요…?)</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23179,20 +23179,20 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>"한 바퀴 더 돌아요"</t>
+          <t>쥐커드 제노사이드!!!</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#cdb4db</t>
         </is>
       </c>
     </row>
@@ -23202,20 +23202,20 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>c16</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>아 진짜요…?</t>
+          <t>쥐커드 리마스터!!!!</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -23225,20 +23225,20 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>c17</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>흐에~</t>
+          <t>★ 치즈 {n}개 후원!</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23248,20 +23248,20 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>c18</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>우다다다다!!</t>
+          <t>★ 큰손 햄찌님 치즈 {n}개 후원!</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -23271,16 +23271,16 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>c19</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>두두두두두!!</t>
+          <t>"쥐커드 리마스터 해줘!!!"</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
@@ -23294,16 +23294,16 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>c20</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>타타타타!!</t>
+          <t>"쥐커드 해주세요!!"</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
@@ -23317,16 +23317,16 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>c21</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>리마스터 들어갑니다!!</t>
+          <t>"이이잉~~ 쥐커드!!"</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
@@ -23340,20 +23340,20 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>c22</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~</t>
+          <t>"믿고 있었다구!! 쥐커드!!"</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23363,20 +23363,20 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>c23</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>탕!</t>
+          <t>"앵콜!! 앵콜!!"</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23386,20 +23386,20 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>c24</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>타타탕!</t>
+          <t>"리마스터 가즈아!!"</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23409,20 +23409,20 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>c25</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>쥐구멍: 쥐커드 고고</t>
+          <t>"효과음 입으로 해주세요"</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23432,20 +23432,20 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>c26</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>찍찍이: 도네 쐈다</t>
+          <t>"엄마가 쥐커드 보래요"</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23455,20 +23455,20 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>c27</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>햄찌팬: ??</t>
+          <t>"한 바퀴 더 돌아요"</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23478,20 +23478,20 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>c28</t>
+          <t>c16</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>치즈러버: 크크크크크크</t>
+          <t>아 진짜요…?</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>#bfe8ff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23501,20 +23501,20 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>c29</t>
+          <t>c17</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>하수구왕: 쥐커드!!!</t>
+          <t>흐에~</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23524,16 +23524,16 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>c30</t>
+          <t>c18</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>안경쥐팬: 안경 번쩍 크크</t>
+          <t>우다다다다!!</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
@@ -23547,16 +23547,16 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>c31</t>
+          <t>c19</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>고양이싫어: 1000원에 이게 되네</t>
+          <t>두두두두두!!</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
@@ -23570,16 +23570,16 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>c32</t>
+          <t>c20</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>쥐구멍: 레전드의 시작</t>
+          <t>타타타타!!</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
@@ -23593,16 +23593,16 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>c33</t>
+          <t>c21</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>햄찌팬: 리마스터 고고</t>
+          <t>리마스터 들어갑니다!!</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
@@ -23616,20 +23616,20 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>c34</t>
+          <t>c22</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>찍찍이: 모션 짜치네 크크</t>
+          <t>흐에~ 후원 감사합니다~</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23639,85 +23639,85 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>c35</t>
+          <t>c23</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>● LIVE 시청자 {n}명</t>
+          <t>탕!</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c24</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>빨리 봐라 이거…</t>
+          <t>타타탕!</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c25</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더!!!!!</t>
+          <t>쥐구멍: 쥐커드 고고</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c26</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Bring me Acorn!</t>
+          <t>찍찍이: 도네 쐈다</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -23727,89 +23727,89 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c27</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>찌리찌리찌리찌리!!</t>
+          <t>햄찌팬: ??</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>#bfe8ff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c28</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>(수고람쥐썬더…)</t>
+          <t>치즈러버: 크크크크크크</t>
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#bfe8ff</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c29</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>(도토리 냠)</t>
+          <t>하수구왕: 쥐커드!!!</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c30</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>…!!</t>
+          <t>안경쥐팬: 안경 번쩍 크크</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -23819,20 +23819,20 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c31</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Bring me Acorn!!</t>
+          <t>고양이싫어: 1000원에 이게 되네</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
@@ -23842,20 +23842,20 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c32</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더!!!</t>
+          <t>쥐구멍: 레전드의 시작</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
@@ -23865,20 +23865,20 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c33</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>찌리찌리!!</t>
+          <t>햄찌팬: 리마스터 고고</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
@@ -23888,20 +23888,20 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c34</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더어어!!</t>
+          <t>찍찍이: 모션 짜치네 크크</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
@@ -23911,89 +23911,89 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>30030</v>
+        <v>30028</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c35</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>(갑분싸)</t>
+          <t>● LIVE 시청자 {n}명</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>우우우~~ 나가라!!</t>
+          <t>빨리 봐라 이거…</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>감사합니다.</t>
+          <t>람쥐썬더!!!!!</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>감사합니다. 감사합니다.</t>
+          <t>Bring me Acorn!</t>
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
@@ -24003,135 +24003,135 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>감사합니다!!!</t>
+          <t>찌리찌리찌리찌리!!</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#bfe8ff</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>(…인정이지)</t>
+          <t>(수고람쥐썬더…)</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>(꾸벅) 줴리 감사합니다</t>
+          <t>(도토리 냠)</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>※ 전설 등급 궁극기 충전 중 ※</t>
+          <t>…!!</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>※ 궁극기 폭주 중 ※</t>
+          <t>Bring me Acorn!!</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>{n}%</t>
+          <t>람쥐썬더!!!</t>
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
@@ -24141,47 +24141,47 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>로딩 중…</t>
+          <t>찌리찌리!!</t>
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>쥐가 네 마리 모이면?</t>
+          <t>람쥐썬더어어!!</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -24191,20 +24191,20 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>쥐포.</t>
+          <t>(갑분싸)</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -24214,20 +24214,20 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>왕이 넘어지면?</t>
+          <t>우우우~~ 나가라!!</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -24237,20 +24237,20 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>킹콩.</t>
+          <t>감사합니다.</t>
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -24260,20 +24260,20 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>c16</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>소가 웃으면?</t>
+          <t>감사합니다. 감사합니다.</t>
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -24283,20 +24283,20 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>c17</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>우하하.</t>
+          <t>감사합니다!!!</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -24306,20 +24306,20 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>c18</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>세상에서 제일 가난한 왕은?</t>
+          <t>(…인정이지)</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -24329,16 +24329,16 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>c19</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>최저임금.</t>
+          <t>(꾸벅) 줴리 감사합니다</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
@@ -24352,20 +24352,20 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>c20</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>바나나가 웃으면?</t>
+          <t>※ 전설 등급 궁극기 충전 중 ※</t>
         </is>
       </c>
       <c r="D229" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -24375,20 +24375,20 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>c21</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>바나나킥.</t>
+          <t>※ 궁극기 폭주 중 ※</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -24398,20 +24398,20 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>c22</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>개가 사람을 가르치면?</t>
+          <t>{n}%</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -24421,20 +24421,20 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>c23</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>개인지도.</t>
+          <t>로딩 중…</t>
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -24444,16 +24444,16 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>c24</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>오, 뭐 한대?</t>
+          <t>쥐가 네 마리 모이면?</t>
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
@@ -24467,16 +24467,16 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>c25</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>궁극기래!!</t>
+          <t>쥐포.</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
@@ -24490,16 +24490,16 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>c26</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>두근두근…</t>
+          <t>왕이 넘어지면?</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -24513,16 +24513,16 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>c27</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>전설 등급이래!</t>
+          <t>킹콩.</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -24536,16 +24536,16 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>c28</t>
+          <t>c16</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>…어?</t>
+          <t>소가 웃으면?</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
@@ -24559,16 +24559,16 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>c29</t>
+          <t>c17</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>왜 멈췄어?</t>
+          <t>우하하.</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -24582,16 +24582,16 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>c30</t>
+          <t>c18</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>고장 났나?</t>
+          <t>세상에서 제일 가난한 왕은?</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -24605,16 +24605,16 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>c31</t>
+          <t>c19</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>어, 떨어진다!</t>
+          <t>최저임금.</t>
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
@@ -24628,16 +24628,16 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>c32</t>
+          <t>c20</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>온다 온다!!</t>
+          <t>바나나가 웃으면?</t>
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -24651,16 +24651,16 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>c33</t>
+          <t>c21</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>이번엔 진짜다!</t>
+          <t>바나나킥.</t>
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -24674,16 +24674,16 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>c34</t>
+          <t>c22</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>999%?!</t>
+          <t>개가 사람을 가르치면?</t>
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -24697,16 +24697,16 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>c35</t>
+          <t>c23</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>(꿀꺽)</t>
+          <t>개인지도.</t>
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
@@ -24720,12 +24720,12 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>c36</t>
+          <t>c24</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>…….</t>
+          <t>오, 뭐 한대?</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
@@ -24743,12 +24743,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>c37</t>
+          <t>c25</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>이게 궁극기야?</t>
+          <t>궁극기래!!</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
@@ -24766,20 +24766,20 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>c38</t>
+          <t>c26</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>……</t>
+          <t>두근두근…</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -24789,12 +24789,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>c39</t>
+          <t>c27</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>우우우~!</t>
+          <t>전설 등급이래!</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
@@ -24802,7 +24802,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -24812,12 +24812,12 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>c40</t>
+          <t>c28</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>나가라!!</t>
+          <t>…어?</t>
         </is>
       </c>
       <c r="D249" s="2" t="n">
@@ -24825,7 +24825,7 @@
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -24835,12 +24835,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>c41</t>
+          <t>c29</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>계란 던져!!</t>
+          <t>왜 멈췄어?</t>
         </is>
       </c>
       <c r="D250" s="2" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>c42</t>
+          <t>c30</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>아니 인사를 왜 해!</t>
+          <t>고장 났나?</t>
         </is>
       </c>
       <c r="D251" s="2" t="n">
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>c43</t>
+          <t>c31</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>계란 맞으면서 감사하대…</t>
+          <t>어, 떨어진다!</t>
         </is>
       </c>
       <c r="D252" s="2" t="n">
@@ -24904,12 +24904,12 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>c44</t>
+          <t>c32</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>뻔뻔한 것 좀 봐!!</t>
+          <t>온다 온다!!</t>
         </is>
       </c>
       <c r="D253" s="2" t="n">
@@ -24927,12 +24927,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>c45</t>
+          <t>c33</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>아 열받네!!</t>
+          <t>이번엔 진짜다!</t>
         </is>
       </c>
       <c r="D254" s="2" t="n">
@@ -24950,12 +24950,12 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>c46</t>
+          <t>c34</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>…근데 인사는 잘하네</t>
+          <t>999%?!</t>
         </is>
       </c>
       <c r="D255" s="2" t="n">
@@ -24973,12 +24973,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>c47</t>
+          <t>c35</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>줴리감사! 줴리감사!</t>
+          <t>(꿀꺽)</t>
         </is>
       </c>
       <c r="D256" s="2" t="n">
@@ -24996,12 +24996,12 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>c48</t>
+          <t>c36</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>…인정.</t>
+          <t>…….</t>
         </is>
       </c>
       <c r="D257" s="2" t="n">
@@ -25019,12 +25019,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>c49</t>
+          <t>c37</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>우우~</t>
+          <t>이게 궁극기야?</t>
         </is>
       </c>
       <c r="D258" s="2" t="n">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25042,20 +25042,20 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>c50</t>
+          <t>c38</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>내려와!!</t>
+          <t>……</t>
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -25065,20 +25065,20 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>c51</t>
+          <t>c39</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>귀뚤</t>
+          <t>우우우~!</t>
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25088,16 +25088,16 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>c52</t>
+          <t>c40</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>(빠직)</t>
+          <t>나가라!!</t>
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -25111,20 +25111,20 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>c53</t>
+          <t>c41</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>딱!</t>
+          <t>계란 던져!!</t>
         </is>
       </c>
       <c r="D262" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25134,20 +25134,20 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>c54</t>
+          <t>c42</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>아니 인사를 왜 해!</t>
         </is>
       </c>
       <c r="D263" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25157,20 +25157,20 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>c55</t>
+          <t>c43</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>펑!</t>
+          <t>계란 맞으면서 감사하대…</t>
         </is>
       </c>
       <c r="D264" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25180,20 +25180,20 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>c56</t>
+          <t>c44</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>뻥!</t>
+          <t>뻔뻔한 것 좀 봐!!</t>
         </is>
       </c>
       <c r="D265" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25203,20 +25203,20 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>c57</t>
+          <t>c45</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>팡!</t>
+          <t>아 열받네!!</t>
         </is>
       </c>
       <c r="D266" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25226,20 +25226,20 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>c58</t>
+          <t>c46</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>랄라~</t>
+          <t>…근데 인사는 잘하네</t>
         </is>
       </c>
       <c r="D267" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25249,20 +25249,20 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>c59</t>
+          <t>c47</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>룰루~</t>
+          <t>줴리감사! 줴리감사!</t>
         </is>
       </c>
       <c r="D268" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25272,20 +25272,20 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>c60</t>
+          <t>c48</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>♡</t>
+          <t>…인정.</t>
         </is>
       </c>
       <c r="D269" s="2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25295,81 +25295,81 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>c61</t>
+          <t>c49</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>~ 감사합니다 ~</t>
+          <t>우우~</t>
         </is>
       </c>
       <c r="D270" s="2" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c50</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>재료는 전부 넣어! 이랴!</t>
+          <t>내려와!!</t>
         </is>
       </c>
       <c r="D271" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c51</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>(보글보글… 이상한 냄새가 난다)</t>
+          <t>귀뚤</t>
         </is>
       </c>
       <c r="D272" s="2" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c52</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>더 넣어!! 전부 다!!</t>
+          <t>(빠직)</t>
         </is>
       </c>
       <c r="D273" s="2" t="n">
@@ -25377,45 +25377,45 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c53</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>완성!! 대왕 치즈 요리!!</t>
+          <t>딱!</t>
         </is>
       </c>
       <c r="D274" s="2" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c54</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>퐁당!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="D275" s="2" t="n">
@@ -25429,16 +25429,16 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c55</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>풍덩!</t>
+          <t>펑!</t>
         </is>
       </c>
       <c r="D276" s="2" t="n">
@@ -25446,22 +25446,22 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c56</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>첨벙!</t>
+          <t>뻥!</t>
         </is>
       </c>
       <c r="D277" s="2" t="n">
@@ -25469,72 +25469,72 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c57</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>재료 {n}개 대왕 치즈 요리!</t>
+          <t>팡!</t>
         </is>
       </c>
       <c r="D278" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c58</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>내 주방 도구!!</t>
+          <t>랄라~</t>
         </is>
       </c>
       <c r="D279" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c59</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>그건 재료가 아니야!</t>
+          <t>룰루~</t>
         </is>
       </c>
       <c r="D280" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
@@ -25544,20 +25544,20 @@
     </row>
     <row r="281">
       <c r="A281" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c60</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>위생 점검은?!</t>
+          <t>♡</t>
         </is>
       </c>
       <c r="D281" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
@@ -25567,24 +25567,24 @@
     </row>
     <row r="282">
       <c r="A282" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c61</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>이랴!</t>
+          <t>~ 감사합니다 ~</t>
         </is>
       </c>
       <c r="D282" s="2" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25594,20 +25594,20 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>소금!</t>
+          <t>재료는 전부 넣어! 이랴!</t>
         </is>
       </c>
       <c r="D283" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25617,20 +25617,20 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>봉주르~</t>
+          <t>(보글보글… 이상한 냄새가 난다)</t>
         </is>
       </c>
       <c r="D284" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25640,200 +25640,200 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>(휘적휘적)</t>
+          <t>더 넣어!! 전부 다!!</t>
         </is>
       </c>
       <c r="D285" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>킥력 증강 운동화… 출력 최대!</t>
+          <t>완성!! 대왕 치즈 요리!!</t>
         </is>
       </c>
       <c r="D286" s="2" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>범인은… 바로 너야!!</t>
+          <t>퐁당!</t>
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>{n}번째 쿠션!</t>
+          <t>풍덩!</t>
         </is>
       </c>
       <c r="D288" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>단서 {n}개 = 추가 쿠션!</t>
+          <t>첨벙!</t>
         </is>
       </c>
       <c r="D289" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>수수께끼는 모두 풀렸다.</t>
+          <t>재료 {n}개 대왕 치즈 요리!</t>
         </is>
       </c>
       <c r="D290" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>(공은 경찰이 압수해 갔다)</t>
+          <t>내 주방 도구!!</t>
         </is>
       </c>
       <c r="D291" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>{n}연타!</t>
+          <t>그건 재료가 아니야!</t>
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>위생 점검은?!</t>
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
@@ -25843,89 +25843,89 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>총 {n}연타!</t>
+          <t>이랴!</t>
         </is>
       </c>
       <c r="D294" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="n">
-        <v>30033</v>
+        <v>30031</v>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
+          <t>소금!</t>
         </is>
       </c>
       <c r="D295" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="n">
-        <v>30033</v>
+        <v>30031</v>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>삭-제!! 회전회오리이이!!</t>
+          <t>봉주르~</t>
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="n">
-        <v>30033</v>
+        <v>30031</v>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>핵꿀밤!</t>
+          <t>(휘적휘적)</t>
         </is>
       </c>
       <c r="D297" s="2" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -25935,89 +25935,89 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>{n}회전… 양호!</t>
+          <t>킥력 증강 운동화… 출력 최대!</t>
         </is>
       </c>
       <c r="D298" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>양호띠!! (엄지 척)</t>
+          <t>범인은… 바로 너야!!</t>
         </is>
       </c>
       <c r="D299" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>스읍- Miss.</t>
+          <t>{n}번째 쿠션!</t>
         </is>
       </c>
       <c r="D300" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>쌉전드…</t>
+          <t>단서 {n}개 = 추가 쿠션!</t>
         </is>
       </c>
       <c r="D301" s="2" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -26027,70 +26027,415 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>여기 어디야? 천국이네~</t>
+          <t>수수께끼는 모두 풀렸다.</t>
         </is>
       </c>
       <c r="D302" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>컷.</t>
+          <t>(공은 경찰이 압수해 갔다)</t>
         </is>
       </c>
       <c r="D303" s="2" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>c7</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>{n}연타!</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>#fffaf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>c8</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>쾅!</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>30032</v>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>c9</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>총 {n}연타!</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>#8fb3d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
         <v>30033</v>
       </c>
-      <c r="B304" s="2" t="inlineStr">
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>#e8786a</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>삭-제!! 회전회오리이이!!</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>#f2c94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>핵꿀밤!</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>{n}회전… 양호!</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>#fff3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>c5</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>양호띠!! (엄지 척)</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>#f2c94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>c6</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>스읍- Miss.</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>#9aa0a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>c7</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>쌉전드…</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>#f2c94c</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>c8</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>여기 어디야? 천국이네~</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>c9</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>컷.</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>c10</t>
         </is>
       </c>
-      <c r="C304" s="2" t="inlineStr">
+      <c r="C316" s="2" t="inlineStr">
         <is>
           <t>(치즈분수 참사 2탄)</t>
         </is>
       </c>
-      <c r="D304" s="2" t="n">
+      <c r="D316" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="E304" s="2" t="inlineStr">
+      <c r="E316" s="2" t="inlineStr">
         <is>
           <t>#9aa0a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>c11</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>미끄덩!</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>#ffd84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>c12</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>아 거기 치즈 웅덩이 있어요~</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>#fff3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>c13</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>치즈 분수 가동!</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -19198,7 +19198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22393,47 +22393,47 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>30023</v>
+        <v>30022</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>만세! 만만세!</t>
+          <t>전원 포위! 꼬리도 들고!</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#E03D40</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>30023</v>
+        <v>30022</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>(불꽃놀이 안전 수칙: 무시)</t>
+          <t>체포 완료! 찍?!</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#FFFFFF</t>
         </is>
       </c>
     </row>
@@ -22443,12 +22443,12 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>(옆으로 쏘면 안 됩니다)</t>
+          <t>만세! 만만세!</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -22466,12 +22466,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>만만만세!!!</t>
+          <t>(불꽃놀이 안전 수칙: 무시)</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -22489,35 +22489,35 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>앗 뜨거!</t>
+          <t>(옆으로 쏘면 안 됩니다)</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>30024</v>
+        <v>30023</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>짐의 피라미드를 받들라!</t>
+          <t>만만만세!!!</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -22525,30 +22525,30 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>30024</v>
+        <v>30023</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>※ 다단계 아닙니다 (진짜로)</t>
+          <t>앗 뜨거!</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -22558,12 +22558,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>치즈는 전부 꼭대기로~</t>
+          <t>짐의 피라미드를 받들라!</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -22581,20 +22581,20 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>피라미드… 팽이!!</t>
+          <t>※ 다단계 아닙니다 (진짜로)</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -22604,16 +22604,16 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>(짐도 멈추는 법을 모른다)</t>
+          <t>치즈는 전부 꼭대기로~</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
@@ -22627,20 +22627,20 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>(어지러워…)</t>
+          <t>피라미드… 팽이!!</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -22650,20 +22650,20 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>상납!</t>
+          <t>(짐도 멈추는 법을 모른다)</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -22673,66 +22673,66 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>짐에게 바쳐라!</t>
+          <t>(어지러워…)</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>전설의 검을 뽑는 자, 왕이 되리라…</t>
+          <t>상납!</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>30025</v>
+        <v>30024</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>…바위까지 딸려 나왔다.</t>
+          <t>짐에게 바쳐라!</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -22742,12 +22742,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>그냥 이걸로 친다!!</t>
+          <t>전설의 검을 뽑는 자, 왕이 되리라…</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
@@ -22765,20 +22765,20 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>(멈추는 법은 안 배웠다)</t>
+          <t>…바위까지 딸려 나왔다.</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -22788,12 +22788,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>(이제야 진짜 검)</t>
+          <t>그냥 이걸로 친다!!</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -22811,20 +22811,20 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>끄응…</t>
+          <t>(멈추는 법은 안 배웠다)</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
@@ -22834,20 +22834,20 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>끄으응…!</t>
+          <t>(이제야 진짜 검)</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -22857,16 +22857,16 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>끄으으으응!!!</t>
+          <t>끄응…</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -22876,47 +22876,47 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>30026</v>
+        <v>30025</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>(램프를 문지른다… 쓱쓱)</t>
+          <t>끄으응…!</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>30026</v>
+        <v>30025</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>소원을 말해 보거라~!!</t>
+          <t>끄으으으응!!!</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>#cdb4db</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -22926,12 +22926,12 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>소원 1번: 물건 크게 해줘!</t>
+          <t>(램프를 문지른다… 쓱쓱)</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>#cdb4db</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -22949,20 +22949,20 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>소원 2번: 더 많이!!</t>
+          <t>소원을 말해 보거라~!!</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#cdb4db</t>
         </is>
       </c>
     </row>
@@ -22972,12 +22972,12 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>소원 3번: …다 없어져라?</t>
+          <t>소원 1번: 물건 크게 해줘!</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#cdb4db</t>
         </is>
       </c>
     </row>
@@ -22995,20 +22995,20 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>(지니가 곡해함)</t>
+          <t>소원 2번: 더 많이!!</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -23018,62 +23018,62 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>펑!</t>
+          <t>소원 3번: …다 없어져라?</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>30027</v>
+        <v>30026</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>표본 채집 개시. 삐리.</t>
+          <t>(지니가 곡해함)</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>30027</v>
+        <v>30026</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>표본 부족. 더 채집한다. 삐리.</t>
+          <t>펑!</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -23087,12 +23087,12 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>검사 완료. 반납합니다.</t>
+          <t>표본 채집 개시. 삐리.</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -23110,35 +23110,35 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>앗, 나는 빼줘!!</t>
+          <t>표본 부족. 더 채집한다. 삐리.</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>● LIVE · 흐에~ 방송 중~</t>
+          <t>검사 완료. 반납합니다.</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
@@ -23152,16 +23152,16 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>30028</v>
+        <v>30027</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>(아 진짜요…?)</t>
+          <t>앗, 나는 빼줘!!</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
@@ -23179,20 +23179,20 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>쥐커드 제노사이드!!!</t>
+          <t>● LIVE · 흐에~ 방송 중~</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>#cdb4db</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23202,20 +23202,20 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>쥐커드 리마스터!!!!</t>
+          <t>(아 진짜요…?)</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23225,20 +23225,20 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>★ 치즈 {n}개 후원!</t>
+          <t>쥐커드 제노사이드!!!</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#cdb4db</t>
         </is>
       </c>
     </row>
@@ -23248,16 +23248,16 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>★ 큰손 햄찌님 치즈 {n}개 후원!</t>
+          <t>쥐커드 리마스터!!!!</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
@@ -23271,20 +23271,20 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>"쥐커드 리마스터 해줘!!!"</t>
+          <t>★ 치즈 {n}개 후원!</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23294,20 +23294,20 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>"쥐커드 해주세요!!"</t>
+          <t>★ 큰손 햄찌님 치즈 {n}개 후원!</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -23317,16 +23317,16 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>"이이잉~~ 쥐커드!!"</t>
+          <t>"쥐커드 리마스터 해줘!!!"</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
@@ -23340,12 +23340,12 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>"믿고 있었다구!! 쥐커드!!"</t>
+          <t>"쥐커드 해주세요!!"</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
@@ -23363,12 +23363,12 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>"앵콜!! 앵콜!!"</t>
+          <t>"이이잉~~ 쥐커드!!"</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
@@ -23386,12 +23386,12 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>"리마스터 가즈아!!"</t>
+          <t>"믿고 있었다구!! 쥐커드!!"</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
@@ -23409,12 +23409,12 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>"효과음 입으로 해주세요"</t>
+          <t>"앵콜!! 앵콜!!"</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
@@ -23432,12 +23432,12 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>"엄마가 쥐커드 보래요"</t>
+          <t>"리마스터 가즈아!!"</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
@@ -23455,12 +23455,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>"한 바퀴 더 돌아요"</t>
+          <t>"효과음 입으로 해주세요"</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
@@ -23478,16 +23478,16 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>c16</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>아 진짜요…?</t>
+          <t>"엄마가 쥐커드 보래요"</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -23501,16 +23501,16 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>c17</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>흐에~</t>
+          <t>"한 바퀴 더 돌아요"</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
@@ -23524,12 +23524,12 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>c18</t>
+          <t>c16</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>우다다다다!!</t>
+          <t>아 진짜요…?</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
@@ -23547,12 +23547,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>c19</t>
+          <t>c17</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>두두두두두!!</t>
+          <t>흐에~</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
@@ -23570,12 +23570,12 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>c20</t>
+          <t>c18</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>타타타타!!</t>
+          <t>우다다다다!!</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
@@ -23593,12 +23593,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>c21</t>
+          <t>c19</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>리마스터 들어갑니다!!</t>
+          <t>두두두두두!!</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
@@ -23616,20 +23616,20 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>c22</t>
+          <t>c20</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>흐에~ 후원 감사합니다~</t>
+          <t>타타타타!!</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23639,20 +23639,20 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>c23</t>
+          <t>c21</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>탕!</t>
+          <t>리마스터 들어갑니다!!</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -23662,16 +23662,16 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>c24</t>
+          <t>c22</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>타타탕!</t>
+          <t>흐에~ 후원 감사합니다~</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -23685,20 +23685,20 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>c25</t>
+          <t>c23</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>쥐구멍: 쥐커드 고고</t>
+          <t>탕!</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23708,16 +23708,16 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>c26</t>
+          <t>c24</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>찍찍이: 도네 쐈다</t>
+          <t>타타탕!</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -23731,12 +23731,12 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>c27</t>
+          <t>c25</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>햄찌팬: ??</t>
+          <t>쥐구멍: 쥐커드 고고</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -23754,12 +23754,12 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>c28</t>
+          <t>c26</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>치즈러버: 크크크크크크</t>
+          <t>찍찍이: 도네 쐈다</t>
         </is>
       </c>
       <c r="D203" s="2" t="n">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>#bfe8ff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23777,12 +23777,12 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>c29</t>
+          <t>c27</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>하수구왕: 쥐커드!!!</t>
+          <t>햄찌팬: ??</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -23800,12 +23800,12 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>c30</t>
+          <t>c28</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>안경쥐팬: 안경 번쩍 크크</t>
+          <t>치즈러버: 크크크크크크</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
@@ -23813,7 +23813,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#bfe8ff</t>
         </is>
       </c>
     </row>
@@ -23823,12 +23823,12 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>c31</t>
+          <t>c29</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>고양이싫어: 1000원에 이게 되네</t>
+          <t>하수구왕: 쥐커드!!!</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -23846,12 +23846,12 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>c32</t>
+          <t>c30</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>쥐구멍: 레전드의 시작</t>
+          <t>안경쥐팬: 안경 번쩍 크크</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
@@ -23869,12 +23869,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>c33</t>
+          <t>c31</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>햄찌팬: 리마스터 고고</t>
+          <t>고양이싫어: 1000원에 이게 되네</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
@@ -23892,12 +23892,12 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>c34</t>
+          <t>c32</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>찍찍이: 모션 짜치네 크크</t>
+          <t>쥐구멍: 레전드의 시작</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
@@ -23915,66 +23915,66 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>c35</t>
+          <t>c33</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>● LIVE 시청자 {n}명</t>
+          <t>햄찌팬: 리마스터 고고</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c34</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>빨리 봐라 이거…</t>
+          <t>찍찍이: 모션 짜치네 크크</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>30029</v>
+        <v>30028</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c35</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더!!!!!</t>
+          <t>● LIVE 시청자 {n}명</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -23984,12 +23984,12 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Bring me Acorn!</t>
+          <t>빨리 봐라 이거…</t>
         </is>
       </c>
       <c r="D213" s="2" t="n">
@@ -23997,7 +23997,7 @@
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -24007,20 +24007,20 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>찌리찌리찌리찌리!!</t>
+          <t>람쥐썬더!!!!!</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>#bfe8ff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -24030,20 +24030,20 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>(수고람쥐썬더…)</t>
+          <t>Bring me Acorn!</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -24053,20 +24053,20 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>(도토리 냠)</t>
+          <t>찌리찌리찌리찌리!!</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#bfe8ff</t>
         </is>
       </c>
     </row>
@@ -24076,20 +24076,20 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>…!!</t>
+          <t>(수고람쥐썬더…)</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -24099,12 +24099,12 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Bring me Acorn!!</t>
+          <t>(도토리 냠)</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
@@ -24122,12 +24122,12 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더!!!</t>
+          <t>…!!</t>
         </is>
       </c>
       <c r="D219" s="2" t="n">
@@ -24145,12 +24145,12 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>찌리찌리!!</t>
+          <t>Bring me Acorn!!</t>
         </is>
       </c>
       <c r="D220" s="2" t="n">
@@ -24168,12 +24168,12 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>람쥐썬더어어!!</t>
+          <t>람쥐썬더!!!</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
@@ -24187,47 +24187,47 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>(갑분싸)</t>
+          <t>찌리찌리!!</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>30030</v>
+        <v>30029</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>우우우~~ 나가라!!</t>
+          <t>람쥐썬더어어!!</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -24237,20 +24237,20 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>감사합니다.</t>
+          <t>(갑분싸)</t>
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -24260,20 +24260,20 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>감사합니다. 감사합니다.</t>
+          <t>우우우~~ 나가라!!</t>
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -24283,16 +24283,16 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>감사합니다!!!</t>
+          <t>감사합니다.</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -24306,16 +24306,16 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>(…인정이지)</t>
+          <t>감사합니다. 감사합니다.</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -24329,20 +24329,20 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>(꾸벅) 줴리 감사합니다</t>
+          <t>감사합니다!!!</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -24352,20 +24352,20 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>※ 전설 등급 궁극기 충전 중 ※</t>
+          <t>(…인정이지)</t>
         </is>
       </c>
       <c r="D229" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>#f2c14e</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -24375,20 +24375,20 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>※ 궁극기 폭주 중 ※</t>
+          <t>(꾸벅) 줴리 감사합니다</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -24398,20 +24398,20 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>{n}%</t>
+          <t>※ 전설 등급 궁극기 충전 중 ※</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c14e</t>
         </is>
       </c>
     </row>
@@ -24421,20 +24421,20 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>로딩 중…</t>
+          <t>※ 궁극기 폭주 중 ※</t>
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>#dfefff</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -24444,20 +24444,20 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>쥐가 네 마리 모이면?</t>
+          <t>{n}%</t>
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -24467,20 +24467,20 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>쥐포.</t>
+          <t>로딩 중…</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#dfefff</t>
         </is>
       </c>
     </row>
@@ -24490,12 +24490,12 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>왕이 넘어지면?</t>
+          <t>쥐가 네 마리 모이면?</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
@@ -24513,12 +24513,12 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>킹콩.</t>
+          <t>쥐포.</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
@@ -24536,12 +24536,12 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>c16</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>소가 웃으면?</t>
+          <t>왕이 넘어지면?</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
@@ -24559,12 +24559,12 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>c17</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>우하하.</t>
+          <t>킹콩.</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
@@ -24582,12 +24582,12 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>c18</t>
+          <t>c16</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>세상에서 제일 가난한 왕은?</t>
+          <t>소가 웃으면?</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
@@ -24605,12 +24605,12 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>c19</t>
+          <t>c17</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>최저임금.</t>
+          <t>우하하.</t>
         </is>
       </c>
       <c r="D240" s="2" t="n">
@@ -24628,12 +24628,12 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>c20</t>
+          <t>c18</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>바나나가 웃으면?</t>
+          <t>세상에서 제일 가난한 왕은?</t>
         </is>
       </c>
       <c r="D241" s="2" t="n">
@@ -24651,12 +24651,12 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>c21</t>
+          <t>c19</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>바나나킥.</t>
+          <t>최저임금.</t>
         </is>
       </c>
       <c r="D242" s="2" t="n">
@@ -24674,12 +24674,12 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>c22</t>
+          <t>c20</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>개가 사람을 가르치면?</t>
+          <t>바나나가 웃으면?</t>
         </is>
       </c>
       <c r="D243" s="2" t="n">
@@ -24697,12 +24697,12 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>c23</t>
+          <t>c21</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>개인지도.</t>
+          <t>바나나킥.</t>
         </is>
       </c>
       <c r="D244" s="2" t="n">
@@ -24720,16 +24720,16 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>c24</t>
+          <t>c22</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>오, 뭐 한대?</t>
+          <t>개가 사람을 가르치면?</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
@@ -24743,16 +24743,16 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>c25</t>
+          <t>c23</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>궁극기래!!</t>
+          <t>개인지도.</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -24766,12 +24766,12 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>c26</t>
+          <t>c24</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>두근두근…</t>
+          <t>오, 뭐 한대?</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
@@ -24789,12 +24789,12 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>c27</t>
+          <t>c25</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>전설 등급이래!</t>
+          <t>궁극기래!!</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
@@ -24812,12 +24812,12 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>c28</t>
+          <t>c26</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>…어?</t>
+          <t>두근두근…</t>
         </is>
       </c>
       <c r="D249" s="2" t="n">
@@ -24835,12 +24835,12 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>c29</t>
+          <t>c27</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>왜 멈췄어?</t>
+          <t>전설 등급이래!</t>
         </is>
       </c>
       <c r="D250" s="2" t="n">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>c30</t>
+          <t>c28</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>고장 났나?</t>
+          <t>…어?</t>
         </is>
       </c>
       <c r="D251" s="2" t="n">
@@ -24881,12 +24881,12 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>c31</t>
+          <t>c29</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>어, 떨어진다!</t>
+          <t>왜 멈췄어?</t>
         </is>
       </c>
       <c r="D252" s="2" t="n">
@@ -24904,12 +24904,12 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>c32</t>
+          <t>c30</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>온다 온다!!</t>
+          <t>고장 났나?</t>
         </is>
       </c>
       <c r="D253" s="2" t="n">
@@ -24927,12 +24927,12 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>c33</t>
+          <t>c31</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>이번엔 진짜다!</t>
+          <t>어, 떨어진다!</t>
         </is>
       </c>
       <c r="D254" s="2" t="n">
@@ -24950,12 +24950,12 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>c34</t>
+          <t>c32</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>999%?!</t>
+          <t>온다 온다!!</t>
         </is>
       </c>
       <c r="D255" s="2" t="n">
@@ -24973,12 +24973,12 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>c35</t>
+          <t>c33</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>(꿀꺽)</t>
+          <t>이번엔 진짜다!</t>
         </is>
       </c>
       <c r="D256" s="2" t="n">
@@ -24996,12 +24996,12 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>c36</t>
+          <t>c34</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>…….</t>
+          <t>999%?!</t>
         </is>
       </c>
       <c r="D257" s="2" t="n">
@@ -25019,12 +25019,12 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>c37</t>
+          <t>c35</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>이게 궁극기야?</t>
+          <t>(꿀꺽)</t>
         </is>
       </c>
       <c r="D258" s="2" t="n">
@@ -25042,20 +25042,20 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>c38</t>
+          <t>c36</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>……</t>
+          <t>…….</t>
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25065,12 +25065,12 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>c39</t>
+          <t>c37</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>우우우~!</t>
+          <t>이게 궁극기야?</t>
         </is>
       </c>
       <c r="D260" s="2" t="n">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25088,20 +25088,20 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>c40</t>
+          <t>c38</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>나가라!!</t>
+          <t>……</t>
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -25111,12 +25111,12 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>c41</t>
+          <t>c39</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>계란 던져!!</t>
+          <t>우우우~!</t>
         </is>
       </c>
       <c r="D262" s="2" t="n">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25134,12 +25134,12 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>c42</t>
+          <t>c40</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>아니 인사를 왜 해!</t>
+          <t>나가라!!</t>
         </is>
       </c>
       <c r="D263" s="2" t="n">
@@ -25147,7 +25147,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25157,12 +25157,12 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>c43</t>
+          <t>c41</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>계란 맞으면서 감사하대…</t>
+          <t>계란 던져!!</t>
         </is>
       </c>
       <c r="D264" s="2" t="n">
@@ -25180,12 +25180,12 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>c44</t>
+          <t>c42</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>뻔뻔한 것 좀 봐!!</t>
+          <t>아니 인사를 왜 해!</t>
         </is>
       </c>
       <c r="D265" s="2" t="n">
@@ -25203,12 +25203,12 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>c45</t>
+          <t>c43</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>아 열받네!!</t>
+          <t>계란 맞으면서 감사하대…</t>
         </is>
       </c>
       <c r="D266" s="2" t="n">
@@ -25226,12 +25226,12 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>c46</t>
+          <t>c44</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>…근데 인사는 잘하네</t>
+          <t>뻔뻔한 것 좀 봐!!</t>
         </is>
       </c>
       <c r="D267" s="2" t="n">
@@ -25249,12 +25249,12 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>c47</t>
+          <t>c45</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>줴리감사! 줴리감사!</t>
+          <t>아 열받네!!</t>
         </is>
       </c>
       <c r="D268" s="2" t="n">
@@ -25272,12 +25272,12 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>c48</t>
+          <t>c46</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>…인정.</t>
+          <t>…근데 인사는 잘하네</t>
         </is>
       </c>
       <c r="D269" s="2" t="n">
@@ -25295,12 +25295,12 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>c49</t>
+          <t>c47</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>우우~</t>
+          <t>줴리감사! 줴리감사!</t>
         </is>
       </c>
       <c r="D270" s="2" t="n">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25318,12 +25318,12 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>c50</t>
+          <t>c48</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>내려와!!</t>
+          <t>…인정.</t>
         </is>
       </c>
       <c r="D271" s="2" t="n">
@@ -25331,7 +25331,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25341,20 +25341,20 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>c51</t>
+          <t>c49</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>귀뚤</t>
+          <t>우우~</t>
         </is>
       </c>
       <c r="D272" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>#c8c3d0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25364,16 +25364,16 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>c52</t>
+          <t>c50</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>(빠직)</t>
+          <t>내려와!!</t>
         </is>
       </c>
       <c r="D273" s="2" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -25387,20 +25387,20 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>c53</t>
+          <t>c51</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>딱!</t>
+          <t>귀뚤</t>
         </is>
       </c>
       <c r="D274" s="2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#c8c3d0</t>
         </is>
       </c>
     </row>
@@ -25410,20 +25410,20 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>c54</t>
+          <t>c52</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>퍽!</t>
+          <t>(빠직)</t>
         </is>
       </c>
       <c r="D275" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -25433,12 +25433,12 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>c55</t>
+          <t>c53</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>펑!</t>
+          <t>딱!</t>
         </is>
       </c>
       <c r="D276" s="2" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -25456,12 +25456,12 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>c56</t>
+          <t>c54</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>뻥!</t>
+          <t>퍽!</t>
         </is>
       </c>
       <c r="D277" s="2" t="n">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -25479,12 +25479,12 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>c57</t>
+          <t>c55</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>팡!</t>
+          <t>펑!</t>
         </is>
       </c>
       <c r="D278" s="2" t="n">
@@ -25502,20 +25502,20 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>c58</t>
+          <t>c56</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>랄라~</t>
+          <t>뻥!</t>
         </is>
       </c>
       <c r="D279" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25525,20 +25525,20 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>c59</t>
+          <t>c57</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>룰루~</t>
+          <t>팡!</t>
         </is>
       </c>
       <c r="D280" s="2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25548,12 +25548,12 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>c60</t>
+          <t>c58</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>♡</t>
+          <t>랄라~</t>
         </is>
       </c>
       <c r="D281" s="2" t="n">
@@ -25561,7 +25561,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
@@ -25571,66 +25571,66 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>c61</t>
+          <t>c59</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>~ 감사합니다 ~</t>
+          <t>룰루~</t>
         </is>
       </c>
       <c r="D282" s="2" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c60</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>재료는 전부 넣어! 이랴!</t>
+          <t>♡</t>
         </is>
       </c>
       <c r="D283" s="2" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="n">
-        <v>30031</v>
+        <v>30030</v>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c61</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>(보글보글… 이상한 냄새가 난다)</t>
+          <t>~ 감사합니다 ~</t>
         </is>
       </c>
       <c r="D284" s="2" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25640,12 +25640,12 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>더 넣어!! 전부 다!!</t>
+          <t>재료는 전부 넣어! 이랴!</t>
         </is>
       </c>
       <c r="D285" s="2" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25663,20 +25663,20 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>완성!! 대왕 치즈 요리!!</t>
+          <t>(보글보글… 이상한 냄새가 난다)</t>
         </is>
       </c>
       <c r="D286" s="2" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -25686,20 +25686,20 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>퐁당!</t>
+          <t>더 넣어!! 전부 다!!</t>
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -25709,20 +25709,20 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>풍덩!</t>
+          <t>완성!! 대왕 치즈 요리!!</t>
         </is>
       </c>
       <c r="D288" s="2" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
@@ -25732,12 +25732,12 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>첨벙!</t>
+          <t>퐁당!</t>
         </is>
       </c>
       <c r="D289" s="2" t="n">
@@ -25755,20 +25755,20 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>재료 {n}개 대왕 치즈 요리!</t>
+          <t>풍덩!</t>
         </is>
       </c>
       <c r="D290" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>#f0c878</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -25778,12 +25778,12 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>내 주방 도구!!</t>
+          <t>첨벙!</t>
         </is>
       </c>
       <c r="D291" s="2" t="n">
@@ -25801,20 +25801,20 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>그건 재료가 아니야!</t>
+          <t>재료 {n}개 대왕 치즈 요리!</t>
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f0c878</t>
         </is>
       </c>
     </row>
@@ -25824,12 +25824,12 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>위생 점검은?!</t>
+          <t>내 주방 도구!!</t>
         </is>
       </c>
       <c r="D293" s="2" t="n">
@@ -25847,12 +25847,12 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>이랴!</t>
+          <t>그건 재료가 아니야!</t>
         </is>
       </c>
       <c r="D294" s="2" t="n">
@@ -25870,12 +25870,12 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>c13</t>
+          <t>c11</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>소금!</t>
+          <t>위생 점검은?!</t>
         </is>
       </c>
       <c r="D295" s="2" t="n">
@@ -25893,12 +25893,12 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>c14</t>
+          <t>c12</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>봉주르~</t>
+          <t>이랴!</t>
         </is>
       </c>
       <c r="D296" s="2" t="n">
@@ -25916,12 +25916,12 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>c15</t>
+          <t>c13</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>(휘적휘적)</t>
+          <t>소금!</t>
         </is>
       </c>
       <c r="D297" s="2" t="n">
@@ -25935,47 +25935,47 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c14</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>킥력 증강 운동화… 출력 최대!</t>
+          <t>봉주르~</t>
         </is>
       </c>
       <c r="D298" s="2" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="n">
-        <v>30032</v>
+        <v>30031</v>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c15</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>범인은… 바로 너야!!</t>
+          <t>(휘적휘적)</t>
         </is>
       </c>
       <c r="D299" s="2" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -25985,16 +25985,16 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>{n}번째 쿠션!</t>
+          <t>킥력 증강 운동화… 출력 최대!</t>
         </is>
       </c>
       <c r="D300" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -26008,20 +26008,20 @@
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>단서 {n}개 = 추가 쿠션!</t>
+          <t>범인은… 바로 너야!!</t>
         </is>
       </c>
       <c r="D301" s="2" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
@@ -26031,20 +26031,20 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>수수께끼는 모두 풀렸다.</t>
+          <t>{n}번째 쿠션!</t>
         </is>
       </c>
       <c r="D302" s="2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
@@ -26054,20 +26054,20 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>(공은 경찰이 압수해 갔다)</t>
+          <t>단서 {n}개 = 추가 쿠션!</t>
         </is>
       </c>
       <c r="D303" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -26077,20 +26077,20 @@
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>{n}연타!</t>
+          <t>수수께끼는 모두 풀렸다.</t>
         </is>
       </c>
       <c r="D304" s="2" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>#fffaf0</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -26100,12 +26100,12 @@
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>쾅!</t>
+          <t>(공은 경찰이 압수해 갔다)</t>
         </is>
       </c>
       <c r="D305" s="2" t="n">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -26123,66 +26123,66 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>총 {n}연타!</t>
+          <t>{n}연타!</t>
         </is>
       </c>
       <c r="D306" s="2" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>#8fb3d7</t>
+          <t>#fffaf0</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>c1</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
+          <t>쾅!</t>
         </is>
       </c>
       <c r="D307" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>#e8786a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="n">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>삭-제!! 회전회오리이이!!</t>
+          <t>총 {n}연타!</t>
         </is>
       </c>
       <c r="D308" s="2" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#8fb3d7</t>
         </is>
       </c>
     </row>
@@ -26192,20 +26192,20 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>c3</t>
+          <t>c1</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>핵꿀밤!</t>
+          <t>치즈로 해주고 대신 먹어주는 쥐, 테스터 쮜입니다.</t>
         </is>
       </c>
       <c r="D309" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#e8786a</t>
         </is>
       </c>
     </row>
@@ -26215,20 +26215,20 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>c4</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>{n}회전… 양호!</t>
+          <t>삭-제!! 회전회오리이이!!</t>
         </is>
       </c>
       <c r="D310" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -26238,20 +26238,20 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>c5</t>
+          <t>c3</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>양호띠!! (엄지 척)</t>
+          <t>핵꿀밤!</t>
         </is>
       </c>
       <c r="D311" s="2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>#f2c94c</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -26261,20 +26261,20 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>c6</t>
+          <t>c4</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>스읍- Miss.</t>
+          <t>{n}회전… 양호!</t>
         </is>
       </c>
       <c r="D312" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#fff3bf</t>
         </is>
       </c>
     </row>
@@ -26284,16 +26284,16 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>c7</t>
+          <t>c5</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>쌉전드…</t>
+          <t>양호띠!! (엄지 척)</t>
         </is>
       </c>
       <c r="D313" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -26307,12 +26307,12 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>c8</t>
+          <t>c6</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>여기 어디야? 천국이네~</t>
+          <t>스읍- Miss.</t>
         </is>
       </c>
       <c r="D314" s="2" t="n">
@@ -26320,7 +26320,7 @@
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -26330,20 +26330,20 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>c9</t>
+          <t>c7</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>컷.</t>
+          <t>쌉전드…</t>
         </is>
       </c>
       <c r="D315" s="2" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>#ffffff</t>
+          <t>#f2c94c</t>
         </is>
       </c>
     </row>
@@ -26353,20 +26353,20 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>c10</t>
+          <t>c8</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>(치즈분수 참사 2탄)</t>
+          <t>여기 어디야? 천국이네~</t>
         </is>
       </c>
       <c r="D316" s="2" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>#9aa0a6</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -26376,20 +26376,20 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>c11</t>
+          <t>c9</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>미끄덩!</t>
+          <t>컷.</t>
         </is>
       </c>
       <c r="D317" s="2" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>#ffd84a</t>
+          <t>#ffffff</t>
         </is>
       </c>
     </row>
@@ -26399,20 +26399,20 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>c12</t>
+          <t>c10</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>아 거기 치즈 웅덩이 있어요~</t>
+          <t>(치즈분수 참사 2탄)</t>
         </is>
       </c>
       <c r="D318" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>#fff3bf</t>
+          <t>#9aa0a6</t>
         </is>
       </c>
     </row>
@@ -26422,18 +26422,64 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
+          <t>c11</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>미끄덩!</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>#ffd84a</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>c12</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>아 거기 치즈 웅덩이 있어요~</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>#fff3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>30033</v>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
           <t>c13</t>
         </is>
       </c>
-      <c r="C319" s="2" t="inlineStr">
+      <c r="C321" s="2" t="inlineStr">
         <is>
           <t>치즈 분수 가동!</t>
         </is>
       </c>
-      <c r="D319" s="2" t="n">
+      <c r="D321" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="E319" s="2" t="inlineStr">
+      <c r="E321" s="2" t="inlineStr">
         <is>
           <t>#f2c94c</t>
         </is>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -26566,7 +26566,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 물건을 부숨</t>
+          <t>그 쥐가 물건을 부숨</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 벽을 무너뜨림</t>
+          <t>그 쥐가 벽을 무너뜨림</t>
         </is>
       </c>
     </row>
@@ -26596,7 +26596,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 특수 액션을 씀</t>
+          <t>그 쥐가 특수 액션을 쓰거나 묘기(백덤블링·트리플 악셀·윈드밀·대포알)를 성공함</t>
         </is>
       </c>
     </row>
@@ -26611,7 +26611,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 부모로 새끼를 낳음</t>
+          <t>그 쥐가 부모로 새끼를 낳음</t>
         </is>
       </c>
     </row>
@@ -26626,7 +26626,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 사람을 날려 퇴근시킴</t>
+          <t>그 쥐가 사람을 날려 퇴근시킴</t>
         </is>
       </c>
     </row>
@@ -26641,7 +26641,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 고양이를 날려버림</t>
+          <t>그 쥐가 고양이를 날려버림</t>
         </is>
       </c>
     </row>
@@ -26656,7 +26656,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>그 종의 쥐가 보스를 때림 (보스 만들 때 연결)</t>
+          <t>그 쥐가 보스를 때림 (보스 만들 때 연결)</t>
         </is>
       </c>
     </row>
@@ -26671,7 +26671,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>층을 넘어감 (필드에 있는 필살기 종 전부)</t>
+          <t>층을 넘어감 (무리의 쥐 전부, 한 마리씩)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G20" s="1" t="n">
         <v>20017</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G21" s="1" t="n">
         <v>20018</v>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G22" s="1" t="n">
         <v>20019</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G23" s="1" t="n">
         <v>20020</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1" t="n">
         <v>20021</v>
@@ -1752,7 +1752,7 @@
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G25" s="1" t="n">
         <v>20022</v>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G26" s="1" t="n">
         <v>20023</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G27" s="1" t="n">
         <v>20024</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G28" s="1" t="n">
         <v>20025</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G29" s="1" t="n">
         <v>20026</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G30" s="1" t="n">
         <v>20027</v>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G31" s="1" t="n">
         <v>20028</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>20029</v>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G33" s="1" t="n">
         <v>20030</v>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G34" s="1" t="n">
         <v>20031</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G35" s="1" t="n">
         <v>20032</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G36" s="1" t="n">
         <v>20033</v>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G37" s="1" t="n">
         <v>20034</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G38" s="1" t="n">
         <v>20035</v>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G39" s="1" t="n">
         <v>20036</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="F40" s="1" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1" t="n">
         <v>20037</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="F41" s="1" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G41" s="1" t="n">
         <v>20038</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G42" s="1" t="n">
         <v>20039</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="G43" s="1" t="n">
         <v>20040</v>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="F44" s="1" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G44" s="1" t="n">
         <v>20041</v>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="F45" s="1" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G45" s="1" t="n">
         <v>20042</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="F46" s="1" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="G46" s="1" t="n">
         <v>20043</v>
@@ -2874,7 +2874,7 @@
         </is>
       </c>
       <c r="F47" s="1" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="G47" s="1" t="n">
         <v>20044</v>
@@ -2925,7 +2925,7 @@
         </is>
       </c>
       <c r="F48" s="1" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G48" s="1" t="n">
         <v>20045</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G49" s="1" t="n">
         <v>20046</v>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="G50" s="1" t="n">
         <v>20047</v>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="G51" s="1" t="n">
         <v>20048</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G52" s="1" t="n">
         <v>20049</v>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="G53" s="1" t="n">
         <v>20050</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="G54" s="1" t="n">
         <v>20051</v>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="G55" s="1" t="n">
         <v>20052</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="G56" s="1" t="n">
         <v>20053</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="F57" s="1" t="n">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="G57" s="1" t="n">
         <v>20054</v>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="G58" s="1" t="n">
         <v>20055</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="G59" s="1" t="n">
         <v>20056</v>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="G60" s="1" t="n">
         <v>20057</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>121</v>
+        <v>289</v>
       </c>
       <c r="G61" s="1" t="n">
         <v>20058</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>99</v>
+        <v>236</v>
       </c>
       <c r="G62" s="1" t="n">
         <v>20059</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="G63" s="1" t="n">
         <v>20060</v>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="G64" s="1" t="n">
         <v>20061</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="G65" s="1" t="n">
         <v>20062</v>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="G66" s="1" t="n">
         <v>20063</v>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="G67" s="1" t="n">
         <v>20064</v>
@@ -3945,7 +3945,7 @@
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>110</v>
+        <v>262</v>
       </c>
       <c r="G68" s="1" t="n">
         <v>20065</v>
@@ -3996,7 +3996,7 @@
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="G69" s="1" t="n">
         <v>20066</v>
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="G70" s="1" t="n">
         <v>20067</v>
@@ -4098,7 +4098,7 @@
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="G71" s="1" t="n">
         <v>20068</v>
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>128</v>
+        <v>378</v>
       </c>
       <c r="G72" s="1" t="n">
         <v>20069</v>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>144</v>
+        <v>425</v>
       </c>
       <c r="G73" s="1" t="n">
         <v>20070</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="G74" s="1" t="n">
         <v>20071</v>
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>112</v>
+        <v>331</v>
       </c>
       <c r="G75" s="1" t="n">
         <v>20072</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>96</v>
+        <v>284</v>
       </c>
       <c r="G76" s="1" t="n">
         <v>20073</v>
@@ -4404,7 +4404,7 @@
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>160</v>
+        <v>472</v>
       </c>
       <c r="G77" s="1" t="n">
         <v>20074</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>144</v>
+        <v>425</v>
       </c>
       <c r="G78" s="1" t="n">
         <v>20075</v>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>176</v>
+        <v>520</v>
       </c>
       <c r="G79" s="1" t="n">
         <v>20076</v>
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>80</v>
+        <v>236</v>
       </c>
       <c r="G80" s="1" t="n">
         <v>20077</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>64</v>
+        <v>189</v>
       </c>
       <c r="G81" s="1" t="n">
         <v>20078</v>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>80</v>
+        <v>236</v>
       </c>
       <c r="G82" s="1" t="n">
         <v>20079</v>
@@ -17517,7 +17517,7 @@
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="1" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="1" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="1" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
       </c>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
@@ -17811,7 +17811,7 @@
       </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="1" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -17913,7 +17913,7 @@
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
       </c>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
       </c>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="1" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="1" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
@@ -18643,7 +18643,7 @@
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
       </c>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="1" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         </is>
       </c>
       <c r="F36" s="1" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -5110,7 +5110,11 @@
           <t>🐀</t>
         </is>
       </c>
-      <c r="T4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20001</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>주변 쥐 1마리당 피해 +6% (최대 10마리)</t>
@@ -5187,7 +5191,11 @@
           <t>📢</t>
         </is>
       </c>
-      <c r="T5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21001</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 6마리 이상 모이면 (20초마다) → 하수구 동창회: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -5264,7 +5272,11 @@
           <t>🧱</t>
         </is>
       </c>
-      <c r="T6" s="2" t="n"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20002</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>벽에 주는 피해 ×3.0</t>
@@ -5341,7 +5353,11 @@
           <t>💨</t>
         </is>
       </c>
-      <c r="T7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21002</t>
+        </is>
+      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>벽을 들이받을 때 12% 확률로 → 벽 틈 질주: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -5418,7 +5434,11 @@
           <t>🌀</t>
         </is>
       </c>
-      <c r="T8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20003</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>돌진 속도 ×1.15, 돌진 박치기 피해 ×1.20</t>
@@ -5495,7 +5515,11 @@
           <t>🌀</t>
         </is>
       </c>
-      <c r="T9" s="2" t="n"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21003</t>
+        </is>
+      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 미로 폭주: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -5572,7 +5596,11 @@
           <t>💢</t>
         </is>
       </c>
-      <c r="T10" s="2" t="n"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20004</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>물건을 ×1.3 세게 날림 (날아간 물건 충돌 피해도 ↑)</t>
@@ -5649,7 +5677,11 @@
           <t>💢</t>
         </is>
       </c>
-      <c r="T11" s="2" t="n"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21004</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>10 콤보 이상일 때 부딪히면 8% 확률로 → 후드 3단 박치기: 3번 뛰어올라 쾅! 내려찍기 (반경 95)</t>
@@ -5726,7 +5758,11 @@
           <t>💞</t>
         </is>
       </c>
-      <c r="T12" s="2" t="n"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20005</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷1.5, 새끼가 윗등급일 확률 ↑</t>
@@ -5803,7 +5839,11 @@
           <t>🏡</t>
         </is>
       </c>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21005</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>새끼를 낳을 때 35% 확률로 → 대가족 상경: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -5880,7 +5920,11 @@
           <t>🌻</t>
         </is>
       </c>
-      <c r="T14" s="2" t="n"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20006</t>
+        </is>
+      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×1.4</t>
@@ -5959,7 +6003,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Props/hamsterball</t>
+          <t>RatSkillIcons/rs_21006</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6038,7 +6082,11 @@
           <t>🐀</t>
         </is>
       </c>
-      <c r="T16" s="2" t="n"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20007</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>주변 쥐 1마리당 피해 +6% (최대 10마리)</t>
@@ -6115,7 +6163,11 @@
           <t>🌙</t>
         </is>
       </c>
-      <c r="T17" s="2" t="n"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21007</t>
+        </is>
+      </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 6마리 이상 모이면 (20초마다) → 다락방 습격: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -6192,7 +6244,11 @@
           <t>🎯</t>
         </is>
       </c>
-      <c r="T18" s="2" t="n"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20008</t>
+        </is>
+      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +8%, 크리티컬 ×3.5</t>
@@ -6269,7 +6325,11 @@
           <t>💨</t>
         </is>
       </c>
-      <c r="T19" s="2" t="n"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21008</t>
+        </is>
+      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 맨몸 돌진: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -6346,7 +6406,11 @@
           <t>🌾</t>
         </is>
       </c>
-      <c r="T20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20009</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t>돌진 속도 ×1.15, 돌진 박치기 피해 ×1.20</t>
@@ -6423,7 +6487,11 @@
           <t>🌾</t>
         </is>
       </c>
-      <c r="T21" s="2" t="n"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21009</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
           <t>벽을 들이받을 때 12% 확률로 → 이삭 줄타기: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -6500,7 +6568,11 @@
           <t>🌻</t>
         </is>
       </c>
-      <c r="T22" s="2" t="n"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20010</t>
+        </is>
+      </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×1.4</t>
@@ -6579,7 +6651,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Props/hamsterball</t>
+          <t>RatSkillIcons/rs_21010</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6658,7 +6730,11 @@
           <t>🌵</t>
         </is>
       </c>
-      <c r="T24" s="2" t="n"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20011</t>
+        </is>
+      </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
           <t>한 번 더 갉을 확률 20%</t>
@@ -6735,7 +6811,11 @@
           <t>🌵</t>
         </is>
       </c>
-      <c r="T25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21011</t>
+        </is>
+      </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
           <t>10 콤보 이상일 때 부딪히면 8% 확률로 → 가시 공 굴리기: 3번 뛰어올라 쾅! 내려찍기 (반경 95)</t>
@@ -6812,7 +6892,11 @@
           <t>🦘</t>
         </is>
       </c>
-      <c r="T26" s="2" t="n"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20012</t>
+        </is>
+      </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
           <t>돌진 속도 ×1.15, 돌진 박치기 피해 ×1.20</t>
@@ -6889,7 +6973,11 @@
           <t>🦘</t>
         </is>
       </c>
-      <c r="T27" s="2" t="n"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21012</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 사막 대점프: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -6966,7 +7054,11 @@
           <t>👂</t>
         </is>
       </c>
-      <c r="T28" s="2" t="n"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20013</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +8%, 크리티컬 ×3.5</t>
@@ -7043,7 +7135,11 @@
           <t>👂</t>
         </is>
       </c>
-      <c r="T29" s="2" t="n"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21013</t>
+        </is>
+      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
           <t>20초마다 → 귀 펄럭 소문 폭탄: 음파 충격파 5번 + 주변 동료 광란 (반경 160)</t>
@@ -7120,7 +7216,11 @@
           <t>🏜️</t>
         </is>
       </c>
-      <c r="T30" s="2" t="n"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20014</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
           <t>벽에 주는 피해 ×3.0</t>
@@ -7197,7 +7297,11 @@
           <t>🏜️</t>
         </is>
       </c>
-      <c r="T31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21014</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t>벽을 들이받을 때 10% 확률로 → 모래 질주: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×3.0)</t>
@@ -7274,7 +7378,11 @@
           <t>🐼</t>
         </is>
       </c>
-      <c r="T32" s="2" t="n"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20015</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때 7% 확률로 몸을 말아 대포알처럼 튕겨다님</t>
@@ -7351,7 +7459,11 @@
           <t>🐼</t>
         </is>
       </c>
-      <c r="T33" s="2" t="n"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21015</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 판다 대왕 구르기: 거대한 공이 되어 3초간 굴러다니며 파괴 (피해 ×2.0)</t>
@@ -7428,7 +7540,11 @@
           <t>😴</t>
         </is>
       </c>
-      <c r="T34" s="2" t="n"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20016</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>자주 잠듦. 자는 동안 코골이 충격파 (반경 75)</t>
@@ -7505,7 +7621,11 @@
           <t>💤</t>
         </is>
       </c>
-      <c r="T35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21016</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>잠들 때 50% 확률로 → 지진 코골이: 음파 충격파 5번 + 주변 동료 광란 (반경 160)</t>
@@ -7582,7 +7702,11 @@
           <t>🌾</t>
         </is>
       </c>
-      <c r="T36" s="2" t="n"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20017</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷1.6, 새끼가 윗등급일 확률 ↑</t>
@@ -7659,7 +7783,11 @@
           <t>🥔</t>
         </is>
       </c>
-      <c r="T37" s="2" t="n"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21017</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>자기가 부순 물건에서 4% 확률로 감자 드랍 → 같은 종이 주우면 → 감자 투척: 주변에 5개 투척 폭격</t>
@@ -7736,7 +7864,11 @@
           <t>🥊</t>
         </is>
       </c>
-      <c r="T38" s="2" t="n"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20018</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>물건을 ×1.4 세게 날림 (날아간 물건 충돌 피해도 ↑)</t>
@@ -7813,7 +7945,11 @@
           <t>🥊</t>
         </is>
       </c>
-      <c r="T39" s="2" t="n"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21018</t>
+        </is>
+      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 어퍼컷: 3번 뛰어올라 쾅! 내려찍기 (반경 100)</t>
@@ -7890,7 +8026,11 @@
           <t>📚</t>
         </is>
       </c>
-      <c r="T40" s="2" t="n"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20019</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +10%, 크리티컬 ×3.6</t>
@@ -7967,7 +8107,11 @@
           <t>🔔</t>
         </is>
       </c>
-      <c r="T41" s="2" t="n"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21019</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>20 콤보 이상일 때 부딪히면 10% 확률로 → 쉬는 시간!: 주변 동료 전원 광란 4.3초 (속도·피해 ×1.5)</t>
@@ -8044,7 +8188,11 @@
           <t>⚗️</t>
         </is>
       </c>
-      <c r="T42" s="2" t="n"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20020</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
           <t>들이받을 때 20% 확률로 폭탄 투척 (반경 83)</t>
@@ -8123,7 +8271,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>Props/flask</t>
+          <t>RatSkillIcons/rs_21020</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -8202,7 +8350,11 @@
           <t>🤓</t>
         </is>
       </c>
-      <c r="T44" s="2" t="n"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20021</t>
+        </is>
+      </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +10%, 크리티컬 ×3.6</t>
@@ -8281,7 +8433,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>Props/pencil</t>
+          <t>RatSkillIcons/rs_21021</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -8360,7 +8512,11 @@
           <t>⛏️</t>
         </is>
       </c>
-      <c r="T46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20022</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
           <t>벽에 주는 피해 ×3.6</t>
@@ -8439,7 +8595,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>Props/hammer</t>
+          <t>RatSkillIcons/rs_21022</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -8518,7 +8674,11 @@
           <t>🔪</t>
         </is>
       </c>
-      <c r="T48" s="2" t="n"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20023</t>
+        </is>
+      </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
           <t>한 번 더 갉을 확률 26%</t>
@@ -8597,7 +8757,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>Props/knife</t>
+          <t>RatSkillIcons/rs_21023</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -8676,7 +8836,11 @@
           <t>🎒</t>
         </is>
       </c>
-      <c r="T50" s="2" t="n"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20024</t>
+        </is>
+      </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×1.5</t>
@@ -8753,7 +8917,11 @@
           <t>🎒</t>
         </is>
       </c>
-      <c r="T51" s="2" t="n"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21024</t>
+        </is>
+      </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 배낭 굴리기: 거대한 공이 되어 3초간 굴러다니며 파괴 (피해 ×2.6)</t>
@@ -8830,7 +8998,11 @@
           <t>✉️</t>
         </is>
       </c>
-      <c r="T52" s="2" t="n"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20025</t>
+        </is>
+      </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
           <t>택배가 떨어질 때 화면에 있으면 자기 주변에 1개 추가 배달</t>
@@ -8909,7 +9081,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>Props/letter</t>
+          <t>RatSkillIcons/rs_21025</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -8988,7 +9160,11 @@
           <t>📦</t>
         </is>
       </c>
-      <c r="T54" s="2" t="n"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20026</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
           <t>택배가 떨어질 때 화면에 있으면 자기 주변에 1개 추가 배달</t>
@@ -9065,7 +9241,11 @@
           <t>🚀</t>
         </is>
       </c>
-      <c r="T55" s="2" t="n"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21026</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>택배 투하 때 화면에 있으면 60% 확률로 → 로켓 배송: 하늘에서 5개 낙하</t>
@@ -9142,7 +9322,11 @@
           <t>🎉</t>
         </is>
       </c>
-      <c r="T56" s="2" t="n"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20027</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때 10% 확률로 전매특허 묘기</t>
@@ -9219,7 +9403,11 @@
           <t>🥳</t>
         </is>
       </c>
-      <c r="T57" s="2" t="n"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21027</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>25 콤보 이상일 때 부딪히면 10% 확률로 → 파티 타임: 주변 동료 전원 광란 4.3초 (속도·피해 ×1.5)</t>
@@ -9296,7 +9484,11 @@
           <t>🧹</t>
         </is>
       </c>
-      <c r="T58" s="2" t="n"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20028</t>
+        </is>
+      </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×1.5</t>
@@ -9373,7 +9565,11 @@
           <t>🧹</t>
         </is>
       </c>
-      <c r="T59" s="2" t="n"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21028</t>
+        </is>
+      </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
           <t>자기가 부순 물건에서 4% 확률로 대걸레 드랍 → 같은 종이 주우면 → 대걸레 스윙: 주변에 5개 투척 폭격</t>
@@ -9450,7 +9646,11 @@
           <t>☕</t>
         </is>
       </c>
-      <c r="T60" s="2" t="n"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20029</t>
+        </is>
+      </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
           <t>한 번 더 갉을 확률 26%</t>
@@ -9527,7 +9727,11 @@
           <t>☕</t>
         </is>
       </c>
-      <c r="T61" s="2" t="n"/>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21029</t>
+        </is>
+      </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
           <t>20초마다 → 커피 한 잔씩: 주변 동료 전원 광란 4.3초 (속도·피해 ×1.5)</t>
@@ -9604,7 +9808,11 @@
           <t>🌱</t>
         </is>
       </c>
-      <c r="T62" s="2" t="n"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20030</t>
+        </is>
+      </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷1.6, 새끼가 윗등급일 확률 ↑</t>
@@ -9681,7 +9889,11 @@
           <t>🌻</t>
         </is>
       </c>
-      <c r="T63" s="2" t="n"/>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21030</t>
+        </is>
+      </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
           <t>새끼를 낳을 때 35% 확률로 → 꽃밭 대가족: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -9758,7 +9970,11 @@
           <t>🎨</t>
         </is>
       </c>
-      <c r="T64" s="2" t="n"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20031</t>
+        </is>
+      </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
           <t>들이받을 때 20% 확률로 폭탄 투척 (반경 83)</t>
@@ -9835,7 +10051,11 @@
           <t>🎨</t>
         </is>
       </c>
-      <c r="T65" s="2" t="n"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21031</t>
+        </is>
+      </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
           <t>자기가 부순 물건에서 4% 확률로 물감 드랍 → 같은 종이 주우면 → 물감 난사: 주변에 5개 투척 폭격</t>
@@ -9912,7 +10132,11 @@
           <t>🛹</t>
         </is>
       </c>
-      <c r="T66" s="2" t="n"/>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20032</t>
+        </is>
+      </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때 10% 확률로 전매특허 묘기</t>
@@ -9991,7 +10215,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>Props/skateboard</t>
+          <t>RatSkillIcons/rs_21032</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -10070,7 +10294,11 @@
           <t>☢️</t>
         </is>
       </c>
-      <c r="T68" s="2" t="n"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20033</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
           <t>주변(반경 70)에 계속 방사능 피해</t>
@@ -10147,7 +10375,11 @@
           <t>☢️</t>
         </is>
       </c>
-      <c r="T69" s="2" t="n"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21033</t>
+        </is>
+      </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
           <t>15 콤보 이상일 때 부딪히면 8% 확률로 → 방사능 폭주: 주변 물건을 빨아들인 뒤 대폭발 (반경 234)</t>
@@ -10224,7 +10456,11 @@
           <t>🧬</t>
         </is>
       </c>
-      <c r="T70" s="2" t="n"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20034</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건은 크게 폭발 (반경 +43)</t>
@@ -10301,7 +10537,11 @@
           <t>🧬</t>
         </is>
       </c>
-      <c r="T71" s="2" t="n"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21034</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 세포 분열: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -10378,7 +10618,11 @@
           <t>💪</t>
         </is>
       </c>
-      <c r="T72" s="2" t="n"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20035</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>물건을 ×1.5 세게 날림 (날아간 물건 충돌 피해도 ↑)</t>
@@ -10455,7 +10699,11 @@
           <t>🏋️</t>
         </is>
       </c>
-      <c r="T73" s="2" t="n"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21035</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 3대 500 던지기: 주변 물건을 번쩍 들어 집어던짐 (충돌 피해 ×5.1)</t>
@@ -10532,7 +10780,11 @@
           <t>🥷</t>
         </is>
       </c>
-      <c r="T74" s="2" t="n"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20036</t>
+        </is>
+      </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
           <t>1.8초마다 순간이동해서 물건을 급습 (피해 ×2)</t>
@@ -10609,7 +10861,11 @@
           <t>🥷</t>
         </is>
       </c>
-      <c r="T75" s="2" t="n"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21036</t>
+        </is>
+      </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 그림자 분신술: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -10686,7 +10942,11 @@
           <t>🎤</t>
         </is>
       </c>
-      <c r="T76" s="2" t="n"/>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20037</t>
+        </is>
+      </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
           <t>반경 180 안의 동료 쥐 피해·속도 +17%</t>
@@ -10763,7 +11023,11 @@
           <t>🎤</t>
         </is>
       </c>
-      <c r="T77" s="2" t="n"/>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21037</t>
+        </is>
+      </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 5마리 이상 모이면 (18초마다) → 게릴라 콘서트: 음파 충격파 5번 + 주변 동료 광란 (반경 174)</t>
@@ -10840,7 +11104,11 @@
           <t>🖱️</t>
         </is>
       </c>
-      <c r="T78" s="2" t="n"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20038</t>
+        </is>
+      </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
           <t>한 번 더 갉을 확률 34%</t>
@@ -10917,7 +11185,11 @@
           <t>🖱️</t>
         </is>
       </c>
-      <c r="T79" s="2" t="n"/>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21038</t>
+        </is>
+      </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 광클 연타: 앞의 물건을 초고속 12연타 (타당 피해 ×1.7)</t>
@@ -10994,7 +11266,11 @@
           <t>🚨</t>
         </is>
       </c>
-      <c r="T80" s="2" t="n"/>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20039</t>
+        </is>
+      </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +14%, 크리티컬 ×3.9</t>
@@ -11071,7 +11347,11 @@
           <t>🚓</t>
         </is>
       </c>
-      <c r="T81" s="2" t="n"/>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21039</t>
+        </is>
+      </c>
       <c r="U81" s="2" t="inlineStr">
         <is>
           <t>20 콤보 이상일 때 부딪히면 8% 확률로 → 지원 요청: 동료 3마리 소환 (6초 동안 함께 난동)</t>
@@ -11148,7 +11428,11 @@
           <t>🪓</t>
         </is>
       </c>
-      <c r="T82" s="2" t="n"/>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20040</t>
+        </is>
+      </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
           <t>벽에 주는 피해 ×4.4</t>
@@ -11227,7 +11511,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>Props/extinguisher</t>
+          <t>RatSkillIcons/rs_21040</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -11306,7 +11590,11 @@
           <t>🏴‍☠️</t>
         </is>
       </c>
-      <c r="T84" s="2" t="n"/>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20041</t>
+        </is>
+      </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×1.7</t>
@@ -11385,7 +11673,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>FX/bomb</t>
+          <t>RatSkillIcons/rs_21041</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -11464,7 +11752,11 @@
           <t>🤠</t>
         </is>
       </c>
-      <c r="T86" s="2" t="n"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20042</t>
+        </is>
+      </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
           <t>물건을 ×1.5 세게 날림 (날아간 물건 충돌 피해도 ↑)</t>
@@ -11543,7 +11835,7 @@
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>Props/lasso</t>
+          <t>RatSkillIcons/rs_21042</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -11622,7 +11914,11 @@
           <t>💉</t>
         </is>
       </c>
-      <c r="T88" s="2" t="n"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20043</t>
+        </is>
+      </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷1.9, 새끼가 윗등급일 확률 ↑</t>
@@ -11699,7 +11995,11 @@
           <t>💉</t>
         </is>
       </c>
-      <c r="T89" s="2" t="n"/>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21043</t>
+        </is>
+      </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
           <t>새끼를 낳을 때 40% 확률로 → 링거 투혼: 주변 동료 전원 광란 4.7초 (속도·피해 ×1.5)</t>
@@ -11776,7 +12076,11 @@
           <t>⛏️</t>
         </is>
       </c>
-      <c r="T90" s="2" t="n"/>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20044</t>
+        </is>
+      </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
           <t>벽에 주는 피해 ×4.4</t>
@@ -11855,7 +12159,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>Props/pickaxe</t>
+          <t>RatSkillIcons/rs_21044</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -11934,7 +12238,11 @@
           <t>👁️</t>
         </is>
       </c>
-      <c r="T92" s="2" t="n"/>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20045</t>
+        </is>
+      </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>1.9초마다 레이저 발사, 물건 3개 관통</t>
@@ -12011,7 +12319,11 @@
           <t>👁️</t>
         </is>
       </c>
-      <c r="T93" s="2" t="n"/>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21045</t>
+        </is>
+      </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
           <t>20초마다 → 360° 레이저: 360° 회전 레이저 (피해 ×4.4)</t>
@@ -12088,7 +12400,11 @@
           <t>💣</t>
         </is>
       </c>
-      <c r="T94" s="2" t="n"/>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20046</t>
+        </is>
+      </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
           <t>들이받을 때 33% 확률로 폭탄 투척 (반경 92)</t>
@@ -12167,7 +12483,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>Props/gun</t>
+          <t>RatSkillIcons/rs_21046</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -12246,7 +12562,11 @@
           <t>🦸</t>
         </is>
       </c>
-      <c r="T96" s="2" t="n"/>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20047</t>
+        </is>
+      </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
           <t>돌진할 때 멈추지 않고 물건을 뚫고 지나감 (피해 ×1.44)</t>
@@ -12323,7 +12643,11 @@
           <t>🦸</t>
         </is>
       </c>
-      <c r="T97" s="2" t="n"/>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21047</t>
+        </is>
+      </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
           <t>10 콤보 이상일 때 부딪히면 8% 확률로 → 초음속 연속 펀치: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×6.6)</t>
@@ -12400,7 +12724,11 @@
           <t>🔍</t>
         </is>
       </c>
-      <c r="T98" s="2" t="n"/>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20048</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +18%, 크리티컬 ×4.1</t>
@@ -12479,7 +12807,7 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>Props/magnifier</t>
+          <t>RatSkillIcons/rs_21048</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -12558,7 +12886,11 @@
           <t>🧟</t>
         </is>
       </c>
-      <c r="T100" s="2" t="n"/>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20049</t>
+        </is>
+      </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
           <t>한 번 더 갉을 확률 44%</t>
@@ -12635,7 +12967,11 @@
           <t>🧟</t>
         </is>
       </c>
-      <c r="T101" s="2" t="n"/>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21049</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 3% 확률로 → 좀비 떼: 동료 4마리 소환 (6초 동안 함께 난동)</t>
@@ -12712,7 +13048,11 @@
           <t>🩰</t>
         </is>
       </c>
-      <c r="T102" s="2" t="n"/>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20050</t>
+        </is>
+      </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때 18% 확률로 전매특허 묘기</t>
@@ -12789,7 +13129,11 @@
           <t>🩰</t>
         </is>
       </c>
-      <c r="T103" s="2" t="n"/>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21050</t>
+        </is>
+      </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
           <t>15 콤보 이상일 때 부딪히면 10% 확률로 → 32회전 그랑 푸에테: 회오리가 되어 휩쓸고 다님 (피해 ×2.2)</t>
@@ -12866,7 +13210,11 @@
           <t>🚀</t>
         </is>
       </c>
-      <c r="T104" s="2" t="n"/>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20051</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때 15% 확률로 몸을 말아 대포알처럼 튕겨다님</t>
@@ -12943,7 +13291,11 @@
           <t>🛰️</t>
         </is>
       </c>
-      <c r="T105" s="2" t="n"/>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21051</t>
+        </is>
+      </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
           <t>22초마다 → 궤도 폭격: 하늘에서 6개 낙하</t>
@@ -13020,7 +13372,11 @@
           <t>🔥</t>
         </is>
       </c>
-      <c r="T106" s="2" t="n"/>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20052</t>
+        </is>
+      </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
           <t>1.7초마다 앞쪽으로 불꽃 (사거리 154)</t>
@@ -13097,7 +13453,11 @@
           <t>🔥</t>
         </is>
       </c>
-      <c r="T107" s="2" t="n"/>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21052</t>
+        </is>
+      </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
           <t>20초마다 → 치즈 브레스: 부채꼴로 휘두르는 브레스 (사거리 214)</t>
@@ -13174,7 +13534,11 @@
           <t>👻</t>
         </is>
       </c>
-      <c r="T108" s="2" t="n"/>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20053</t>
+        </is>
+      </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
           <t>돌진할 때 멈추지 않고 물건을 뚫고 지나감 (피해 ×1.44)</t>
@@ -13251,7 +13615,11 @@
           <t>👻</t>
         </is>
       </c>
-      <c r="T109" s="2" t="n"/>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21053</t>
+        </is>
+      </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
           <t>벽을 들이받을 때 12% 확률로 → 유령 분신: 동료 4마리 소환 (6초 동안 함께 난동)</t>
@@ -13328,7 +13696,11 @@
           <t>😇</t>
         </is>
       </c>
-      <c r="T110" s="2" t="n"/>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20054</t>
+        </is>
+      </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷2.1, 새끼가 윗등급일 확률 ↑</t>
@@ -13405,7 +13777,11 @@
           <t>😇</t>
         </is>
       </c>
-      <c r="T111" s="2" t="n"/>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21054</t>
+        </is>
+      </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
           <t>24초마다 → 천상의 합창: 주변 동료 전원 광란 5.2초 (속도·피해 ×1.5)</t>
@@ -13482,7 +13858,11 @@
           <t>🦖</t>
         </is>
       </c>
-      <c r="T112" s="2" t="n"/>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20055</t>
+        </is>
+      </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
           <t>부딪힐 때마다 쿵! 착지 충격파 (반경 62)</t>
@@ -13559,7 +13939,11 @@
           <t>🦖</t>
         </is>
       </c>
-      <c r="T113" s="2" t="n"/>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21055</t>
+        </is>
+      </c>
       <c r="U113" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 공룡 대지진: 3번 뛰어올라 쾅! 내려찍기 (반경 113)</t>
@@ -13636,7 +14020,11 @@
           <t>🔮</t>
         </is>
       </c>
-      <c r="T114" s="2" t="n"/>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20056</t>
+        </is>
+      </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
           <t>갉은 물건이 12% 확률로 황금으로 변함 (치즈 ×10)</t>
@@ -13715,7 +14103,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>Props/wand</t>
+          <t>RatSkillIcons/rs_21056</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -13794,7 +14182,11 @@
           <t>⚔️</t>
         </is>
       </c>
-      <c r="T116" s="2" t="n"/>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20057</t>
+        </is>
+      </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
           <t>돌진할 때 멈추지 않고 물건을 뚫고 지나감 (피해 ×1.60)</t>
@@ -13871,7 +14263,11 @@
           <t>⚔️</t>
         </is>
       </c>
-      <c r="T117" s="2" t="n"/>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21057</t>
+        </is>
+      </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
           <t>물건에 부딪힐 때 4% 확률로 → 발도술 일섬: 물건 사이를 4번 순간 돌진하며 일섬 (피해 ×9.0)</t>
@@ -13948,7 +14344,11 @@
           <t>🎸</t>
         </is>
       </c>
-      <c r="T118" s="2" t="n"/>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20058</t>
+        </is>
+      </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
           <t>반경 180 안의 동료 쥐 피해·속도 +30%</t>
@@ -14027,7 +14427,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>Props/guitar</t>
+          <t>RatSkillIcons/rs_21058</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -14106,7 +14506,11 @@
           <t>🦇</t>
         </is>
       </c>
-      <c r="T120" s="2" t="n"/>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20059</t>
+        </is>
+      </c>
       <c r="U120" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건은 크게 폭발 (반경 +75)</t>
@@ -14183,7 +14587,11 @@
           <t>🦇</t>
         </is>
       </c>
-      <c r="T121" s="2" t="n"/>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21059</t>
+        </is>
+      </c>
       <c r="U121" s="2" t="inlineStr">
         <is>
           <t>22초마다 → 흡혈 소용돌이: 주변 물건을 빨아들인 뒤 대폭발 (반경 260)</t>
@@ -14260,7 +14668,11 @@
           <t>🎁</t>
         </is>
       </c>
-      <c r="T122" s="2" t="n"/>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20060</t>
+        </is>
+      </c>
       <c r="U122" s="2" t="inlineStr">
         <is>
           <t>택배가 떨어질 때 화면에 있으면 자기 주변에 2개 추가 배달</t>
@@ -14339,7 +14751,7 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>Props/gift</t>
+          <t>RatSkillIcons/rs_21060</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -14418,7 +14830,11 @@
           <t>🧪</t>
         </is>
       </c>
-      <c r="T124" s="2" t="n"/>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20061</t>
+        </is>
+      </c>
       <c r="U124" s="2" t="inlineStr">
         <is>
           <t>들이받을 때 45% 확률로 폭탄 투척 (반경 100)</t>
@@ -14495,7 +14911,11 @@
           <t>🏹</t>
         </is>
       </c>
-      <c r="T125" s="2" t="n"/>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21061</t>
+        </is>
+      </c>
       <c r="U125" s="2" t="inlineStr">
         <is>
           <t>15 콤보 이상일 때 부딪히면 8% 확률로 → 역병 석궁 난사: 주변에 7개 투척 폭격</t>
@@ -14572,7 +14992,11 @@
           <t>👑</t>
         </is>
       </c>
-      <c r="T126" s="2" t="n"/>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20062</t>
+        </is>
+      </c>
       <c r="U126" s="2" t="inlineStr">
         <is>
           <t>반경 180 안의 동료 쥐 피해·속도 +30%</t>
@@ -14649,7 +15073,11 @@
           <t>👑</t>
         </is>
       </c>
-      <c r="T127" s="2" t="n"/>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21062</t>
+        </is>
+      </c>
       <c r="U127" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 5마리 이상 모이면 (16초마다) → 왕의 군대: 동료 5마리 소환 (6초 동안 함께 난동)</t>
@@ -14726,7 +15154,11 @@
           <t>👸</t>
         </is>
       </c>
-      <c r="T128" s="2" t="n"/>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20063</t>
+        </is>
+      </c>
       <c r="U128" s="2" t="inlineStr">
         <is>
           <t>번식 쿨타임 ÷2.5, 새끼가 윗등급일 확률 ↑</t>
@@ -14803,7 +15235,11 @@
           <t>👸</t>
         </is>
       </c>
-      <c r="T129" s="2" t="n"/>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21063</t>
+        </is>
+      </c>
       <c r="U129" s="2" t="inlineStr">
         <is>
           <t>새끼를 낳을 때 40% 확률로 → 여왕의 축복: 주변 동료 전원 광란 6.0초 (속도·피해 ×1.5)</t>
@@ -14880,7 +15316,11 @@
           <t>🪓</t>
         </is>
       </c>
-      <c r="T130" s="2" t="n"/>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20064</t>
+        </is>
+      </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
           <t>물건을 ×1.9 세게 날림 (날아간 물건 충돌 피해도 ↑)</t>
@@ -14959,7 +15399,7 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>Props/axe</t>
+          <t>RatSkillIcons/rs_21064</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
@@ -15038,7 +15478,11 @@
           <t>🤖</t>
         </is>
       </c>
-      <c r="T132" s="2" t="n"/>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20065</t>
+        </is>
+      </c>
       <c r="U132" s="2" t="inlineStr">
         <is>
           <t>1.7초마다 레이저 발사, 물건 4개 관통</t>
@@ -15117,7 +15561,7 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>FX/missile</t>
+          <t>RatSkillIcons/rs_21065</t>
         </is>
       </c>
       <c r="U133" s="2" t="inlineStr">
@@ -15196,7 +15640,11 @@
           <t>🌌</t>
         </is>
       </c>
-      <c r="T134" s="2" t="n"/>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20066</t>
+        </is>
+      </c>
       <c r="U134" s="2" t="inlineStr">
         <is>
           <t>주변(반경 86)에 계속 방사능 피해</t>
@@ -15273,7 +15721,11 @@
           <t>🌌</t>
         </is>
       </c>
-      <c r="T135" s="2" t="n"/>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21066</t>
+        </is>
+      </c>
       <c r="U135" s="2" t="inlineStr">
         <is>
           <t>20 콤보 이상일 때 부딪히면 10% 확률로 → 블랙홀: 주변 물건을 빨아들인 뒤 대폭발 (반경 260)</t>
@@ -15350,7 +15802,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="T136" s="2" t="n"/>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20067</t>
+        </is>
+      </c>
       <c r="U136" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건은 크게 폭발 (반경 +100)</t>
@@ -15427,7 +15883,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="T137" s="2" t="n"/>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21067</t>
+        </is>
+      </c>
       <c r="U137" s="2" t="inlineStr">
         <is>
           <t>18초마다 → 건전지 백만 볼트: 360° 회전 레이저 (피해 ×8.0)</t>
@@ -15504,7 +15964,11 @@
           <t>🎈</t>
         </is>
       </c>
-      <c r="T138" s="2" t="n"/>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20068</t>
+        </is>
+      </c>
       <c r="U138" s="2" t="inlineStr">
         <is>
           <t>반경 180 안의 동료 쥐 피해·속도 +40%</t>
@@ -15581,7 +16045,11 @@
           <t>🎈</t>
         </is>
       </c>
-      <c r="T139" s="2" t="n"/>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21068</t>
+        </is>
+      </c>
       <c r="U139" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 5마리 이상 모이면 (18초마다) → 깜짝 퍼레이드: 주변 동료 전원 광란 7.0초 (속도·피해 ×1.5)</t>
@@ -15658,7 +16126,11 @@
           <t>📜</t>
         </is>
       </c>
-      <c r="T140" s="2" t="n"/>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20069</t>
+        </is>
+      </c>
       <c r="U140" s="2" t="inlineStr">
         <is>
           <t>반경 180 안의 동료 쥐 피해·속도 +40%</t>
@@ -15737,7 +16209,7 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>FX/arrow</t>
+          <t>RatSkillIcons/rs_21069</t>
         </is>
       </c>
       <c r="U141" s="2" t="inlineStr">
@@ -15816,7 +16288,11 @@
           <t>🏺</t>
         </is>
       </c>
-      <c r="T142" s="2" t="n"/>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20070</t>
+        </is>
+      </c>
       <c r="U142" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건 치즈 ×2.6</t>
@@ -15893,7 +16369,11 @@
           <t>🏺</t>
         </is>
       </c>
-      <c r="T143" s="2" t="n"/>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21070</t>
+        </is>
+      </c>
       <c r="U143" s="2" t="inlineStr">
         <is>
           <t>황금 물건을 갉으면 50% 확률로 → 황금의 손: 주변 물건을 전부 황금으로 (반경 240, 치즈 ×10)</t>
@@ -15970,7 +16450,11 @@
           <t>🛡️</t>
         </is>
       </c>
-      <c r="T144" s="2" t="n"/>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20071</t>
+        </is>
+      </c>
       <c r="U144" s="2" t="inlineStr">
         <is>
           <t>돌진할 때 멈추지 않고 물건을 뚫고 지나감 (피해 ×1.80)</t>
@@ -16049,7 +16533,7 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>Props/shield</t>
+          <t>RatSkillIcons/rs_21071</t>
         </is>
       </c>
       <c r="U145" s="2" t="inlineStr">
@@ -16128,7 +16612,11 @@
           <t>💎</t>
         </is>
       </c>
-      <c r="T146" s="2" t="n"/>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20072</t>
+        </is>
+      </c>
       <c r="U146" s="2" t="inlineStr">
         <is>
           <t>갉은 물건이 16% 확률로 황금으로 변함 (치즈 ×10)</t>
@@ -16207,7 +16695,7 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>Props/lamp</t>
+          <t>RatSkillIcons/rs_21072</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -16286,7 +16774,11 @@
           <t>🛸</t>
         </is>
       </c>
-      <c r="T148" s="2" t="n"/>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20073</t>
+        </is>
+      </c>
       <c r="U148" s="2" t="inlineStr">
         <is>
           <t>1.5초마다 레이저 발사, 물건 5개 관통</t>
@@ -16363,7 +16855,11 @@
           <t>🛸</t>
         </is>
       </c>
-      <c r="T149" s="2" t="n"/>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21073</t>
+        </is>
+      </c>
       <c r="U149" s="2" t="inlineStr">
         <is>
           <t>22초마다 → 외계인 친구들: 동료 6마리 소환 (6초 동안 함께 난동)</t>
@@ -16440,7 +16936,11 @@
           <t>🎁</t>
         </is>
       </c>
-      <c r="T150" s="2" t="n"/>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20074</t>
+        </is>
+      </c>
       <c r="U150" s="2" t="inlineStr">
         <is>
           <t>택배가 떨어질 때 화면에 있으면 자기 주변에 3개 추가 배달</t>
@@ -16517,7 +17017,11 @@
           <t>🎙️</t>
         </is>
       </c>
-      <c r="T151" s="2" t="n"/>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21074</t>
+        </is>
+      </c>
       <c r="U151" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 5마리 이상 모이면 (16초마다) → 흐에~ 샤우팅: 음파 충격파 5번 + 주변 동료 광란 (반경 220)</t>
@@ -16594,7 +17098,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="T152" s="2" t="n"/>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20075</t>
+        </is>
+      </c>
       <c r="U152" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건은 크게 폭발 (반경 +100)</t>
@@ -16671,7 +17179,11 @@
           <t>⚡</t>
         </is>
       </c>
-      <c r="T153" s="2" t="n"/>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21075</t>
+        </is>
+      </c>
       <c r="U153" s="2" t="inlineStr">
         <is>
           <t>14초마다 → 람쥐썬더: 두 앞발을 하늘로! 번개 8줄기가 주변 물건에 꽂힘 (피해 ×12.0)</t>
@@ -16748,7 +17260,11 @@
           <t>😏</t>
         </is>
       </c>
-      <c r="T154" s="2" t="n"/>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20076</t>
+        </is>
+      </c>
       <c r="U154" s="2" t="inlineStr">
         <is>
           <t>크리티컬 확률 +32%, 크리티컬 ×5.0</t>
@@ -16825,7 +17341,11 @@
           <t>🎩</t>
         </is>
       </c>
-      <c r="T155" s="2" t="n"/>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21076</t>
+        </is>
+      </c>
       <c r="U155" s="2" t="inlineStr">
         <is>
           <t>주변에 동료가 5마리 이상 모이면 (15초마다) → 감사합니다!!: 주변 동료 전원 광란 7.0초 (속도·피해 ×1.5)</t>
@@ -16902,7 +17422,11 @@
           <t>👨‍🍳</t>
         </is>
       </c>
-      <c r="T156" s="2" t="n"/>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20077</t>
+        </is>
+      </c>
       <c r="U156" s="2" t="inlineStr">
         <is>
           <t>이 쥐가 부순 물건은 크게 폭발 (반경 +100)</t>
@@ -16981,7 +17505,7 @@
       </c>
       <c r="T157" s="2" t="inlineStr">
         <is>
-          <t>Props/knife</t>
+          <t>RatSkillIcons/rs_21077</t>
         </is>
       </c>
       <c r="U157" s="2" t="inlineStr">
@@ -17060,7 +17584,11 @@
           <t>🔍</t>
         </is>
       </c>
-      <c r="T158" s="2" t="n"/>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20078</t>
+        </is>
+      </c>
       <c r="U158" s="2" t="inlineStr">
         <is>
           <t>물건을 부술 때마다 단서 +1. 단서 10개마다 축구공 킥이 한 번 더 튕김 (최대 +6, 필살기 쓰면 초기화)</t>
@@ -17137,7 +17665,11 @@
           <t>☝</t>
         </is>
       </c>
-      <c r="T159" s="2" t="n"/>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21078</t>
+        </is>
+      </c>
       <c r="U159" s="2" t="inlineStr">
         <is>
           <t>10초마다 → 진실은 언제나 하나!: 체력이 가장 높은 물건을 가리켜 강력한 피해 (공격력 ×40)</t>
@@ -17214,7 +17746,11 @@
           <t>🧀</t>
         </is>
       </c>
-      <c r="T160" s="2" t="n"/>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20079</t>
+        </is>
+      </c>
       <c r="U160" s="2" t="inlineStr">
         <is>
           <t>이 쥐의 특수 액션·필살기로 부순 물건 치즈 +100%</t>
@@ -17291,7 +17827,11 @@
           <t>⛲</t>
         </is>
       </c>
-      <c r="T161" s="2" t="n"/>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21079</t>
+        </is>
+      </c>
       <c r="U161" s="2" t="inlineStr">
         <is>
           <t>5초마다 → 치즈 분수: 8방향으로 치즈 탄환 4번 발사 (탄환 피해 ×4)</t>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
@@ -4689,6 +4689,414 @@
       </c>
       <c r="M82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>10080</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>폭탄마 쥐</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>425</v>
+      </c>
+      <c r="G83" s="1" t="n">
+        <v>20080</v>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>30034</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>폭발 마법(이라고 우기는 폭탄)만 배웠다. 하루에 딱 한 발 쏘고 그대로 뻗는다. 안대는 멋으로 찼다.</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Parts/bomber</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>10081</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>쥐4</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>jwipo</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="G84" s="1" t="n">
+        <v>20081</v>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>21081</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>쥐라고 우기는 쥐포. 연탄불에 너무 오래 누워 있었다. 고소한 냄새에 물건들이 정신을 못 차린다. 마요네즈 찍지 마세요.</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Parody/rat_jwipo</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>10082</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>고쳐쓰쥐</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>mechanic</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="G85" s="1" t="n">
+        <v>20082</v>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>21082</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>부서진 물건에서 부품을 주워 동료를 튜닝해 준다. 고친 건 많은데 제대로 돌아가는 건 없다.</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Parts/mechanic</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>10083</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>제국군 쥐</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>trooper</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>102</v>
+      </c>
+      <c r="G86" s="1" t="n">
+        <v>20083</v>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>21083</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>제국 최정예 사격수 출신. 백 발 쏘면 한 발 맞는다. 그래도 맞을 때까지 쏜다.</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Parts/trooper</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>10084</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>폭탄이쥐</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>bombrat</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="G87" s="1" t="n">
+        <v>20084</v>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>21084</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>그냥 폭탄이다. 쥐 무리에 섞여 있으니 쥐인 줄 안다. 심지가 다 타면… 다들 피해.</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Parody/rat_bombrat</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>10085</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>맘스땃쥐</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="G88" s="1" t="n">
+        <v>20085</v>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>21085</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>물건을 부술 때마다 패티를 한 장씩 추가한다. 다섯 장이면 그대로 빅버거 박치기. 칼로리는 신경 안 쓴다.</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Parts/burger</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>10086</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>아이스 퀸 쥐</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>icequeen</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>378</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>20086</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>21086</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>30035</v>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>엘사가 연상되는 얼음 마법사 쥐. 때릴 때마다 생명체를 얼린다. 렛잇고를 부르면 동료 쥐들도 덜덜 떤다.</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Parts/icequeen</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>10087</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>5G</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>fiveg</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>20087</v>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>21087</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>휴대폰을 손에서 놓지 않는 쥐. 5G 속도로 동료를 불러 모은다. 근데 하수구에선 잘 안 터진다.</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Parts/fiveg</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4700,7 +5108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U161"/>
+  <dimension ref="A1:U176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17838,6 +18246,1221 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>20080</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>폭렬 외길</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Power</t>
+        </is>
+      </c>
+      <c r="K162" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L162" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" s="1" t="inlineStr">
+        <is>
+          <t>💥</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20080</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>특수 액션이 없는 대신 필살기에 올인: 필살기 위력 ×2.5. 쓰고 나면 반동으로 4초 기절</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>20081</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>노릇노릇</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>Hit_Item</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="1" t="inlineStr">
+        <is>
+          <t>Grill_Stack</t>
+        </is>
+      </c>
+      <c r="K163" s="1" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L163" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="M163" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" s="1" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20081</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>물건을 갉을 때마다 공격력 +3% (최대 15번 = +45%). 3초 동안 안 갉으면 식음</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>21081</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>고소한 냄새</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="1" t="inlineStr">
+        <is>
+          <t>Savory_Smell</t>
+        </is>
+      </c>
+      <c r="K164" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L164" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="M164" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R164" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S164" s="1" t="inlineStr">
+        <is>
+          <t>♨</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21081</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>8초마다 → 고소한 냄새: 반경 300 안 물건이 5초 동안 받는 피해 +30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>20082</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>부품 줍기</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>Destroy_Item</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="1" t="inlineStr">
+        <is>
+          <t>Part_Collect</t>
+        </is>
+      </c>
+      <c r="K165" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" s="1" t="inlineStr">
+        <is>
+          <t>⚙</t>
+        </is>
+      </c>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20082</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>물건을 부술 때마다 부품 +1 (최대 8개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>21082</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>튜닝 완료</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="1" t="inlineStr">
+        <is>
+          <t>Tune_Up</t>
+        </is>
+      </c>
+      <c r="K166" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L166" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="M166" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="N166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R166" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="S166" s="1" t="inlineStr">
+        <is>
+          <t>🔧</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21082</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>부품 8개가 모이면 → 튜닝 완료: 주변(600)에서 가장 센 동료 공격력 +30% (15초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>20083</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>조준 보정</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="1" t="inlineStr">
+        <is>
+          <t>Aim_Assist</t>
+        </is>
+      </c>
+      <c r="K167" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L167" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" s="1" t="inlineStr">
+        <is>
+          <t>🎯</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20083</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>블래스터 명중률 70%. 빗나갈 때마다 +10% (맞으면 처음으로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>21083</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>블래스터 사격</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="F168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" s="1" t="inlineStr">
+        <is>
+          <t>Blaster_Shot</t>
+        </is>
+      </c>
+      <c r="K168" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L168" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="M168" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N168" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="O168" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="P168" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R168" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="S168" s="1" t="inlineStr">
+        <is>
+          <t>🔫</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21083</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>6초마다 → 블래스터 사격: 가까운 물건에 3발 (발당 ×3). 3발 다 맞으면 추가 피해 +50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>20084</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>타들어가는 심지</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" s="1" t="inlineStr">
+        <is>
+          <t>Burning_Fuse</t>
+        </is>
+      </c>
+      <c r="K169" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="L169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" s="1" t="inlineStr">
+        <is>
+          <t>🧨</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20084</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>태어나고 30초 동안 심지가 조금씩 타들어감</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>21084</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>자폭</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" s="1" t="inlineStr">
+        <is>
+          <t>Self_Destruct</t>
+        </is>
+      </c>
+      <c r="K170" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="L170" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="M170" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R170" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" s="1" t="inlineStr">
+        <is>
+          <t>💣</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21084</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>심지가 다 타면 → 자폭: 가장 가까운 벽으로 돌진해 쾅! (벽 피해 ×60, 반경 220 물건 ×12) 그리고 사라짐. 쳇바퀴 훈련 없이 바로 씀</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>20085</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>패티 추가</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>Destroy_Item</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="1" t="inlineStr">
+        <is>
+          <t>Patty_Stack</t>
+        </is>
+      </c>
+      <c r="K171" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L171" s="1" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M171" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" s="1" t="inlineStr">
+        <is>
+          <t>🍔</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20085</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>물건을 부술 때마다 패티 +1 (최대 5장): 장마다 몸이 두꺼워지고 공격력 +12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>21085</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>빅버거 박치기</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>Hit_Item</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" s="1" t="inlineStr">
+        <is>
+          <t>Patty_Slam</t>
+        </is>
+      </c>
+      <c r="K172" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="L172" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="M172" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="N172" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="O172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R172" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S172" s="1" t="inlineStr">
+        <is>
+          <t>🍔</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21085</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>패티 5장일 때 부딪히면 → 빅버거 박치기: 물건으로 뛰어올라 쾅 (직격 ×15, 반경 160 ×5). 패티는 처음으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>20086</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>서리 축적</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="1" t="inlineStr">
+        <is>
+          <t>Frost_Stack</t>
+        </is>
+      </c>
+      <c r="K173" s="1" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L173" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="M173" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N173" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S173" s="1" t="inlineStr">
+        <is>
+          <t>❄</t>
+        </is>
+      </c>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20086</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>생명체(고양이·보스·사람)를 때릴 때마다 빙결 +1: 스택마다 6% 느려짐. 10스택이면 2초 꽁꽁 (4초 동안 안 맞으면 풀림)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>21086</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>얼음 미사일</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="F174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" s="1" t="inlineStr">
+        <is>
+          <t>Ice_Missile</t>
+        </is>
+      </c>
+      <c r="K174" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L174" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="M174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="O174" s="1" t="n">
+        <v>650</v>
+      </c>
+      <c r="P174" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R174" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S174" s="1" t="inlineStr">
+        <is>
+          <t>🧊</t>
+        </is>
+      </c>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21086</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>20초마다 → 얼음 미사일: 쥐 주위에 고드름 5개 → 때리던 대상(없으면 가까운 생명체·물건)으로 유도 (발당 ×4, 맞으면 빙결 +1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>20087</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>신속한 통신</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="H175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="1" t="inlineStr">
+        <is>
+          <t>Rush_Range_Up</t>
+        </is>
+      </c>
+      <c r="K175" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S175" s="1" t="inlineStr">
+        <is>
+          <t>📶</t>
+        </is>
+      </c>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20087</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>쥐 집결(클릭 총공격) 범위 +30% (5G 가 여러 마리여도 한 번만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>21087</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>데이터 전송</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>Ally_Count</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F176" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="G176" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="H176" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" s="1" t="inlineStr">
+        <is>
+          <t>Data_Boost</t>
+        </is>
+      </c>
+      <c r="K176" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L176" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M176" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="N176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R176" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="S176" s="1" t="inlineStr">
+        <is>
+          <t>📱</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21087</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>주변(250)에 동료 5마리 이상이면 (15초마다) → 데이터 전송: 반경 250 쥐 공격력 +25% (8초)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17849,7 +19472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19727,6 +21350,112 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>익스플로전</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UltExplosion</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>영창하는 동안 물건이 가장 많은 쪽 바닥에 붉은 마법진이 커짐 → 초거대 폭발 → 반동으로 털썩 쓰러져 기절 (폭렬 외길 밸류_02 초)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>NewRats/magic_circle, NewRats/explosion_big</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>UltIcons/ult_30034</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>내 이름은 찍구밍! 최강의 폭렬 마법을 다루는 쥐!</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>폭발은 예술이다!</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>#e0524a</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>explosion</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>렛잇고 (Rat it go)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>UltRatItGo</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>얼음성을 맵에 크게 소환 + 눈보라 4.2초: 맵의 생명체(고양이·보스·사람) 전부 빙결 풀스택(꽁꽁), 끝나고 1.5초 더. 성이 내려앉을 때 화면 물건에 서리 충격</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>NewRats/ice_castle</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>UltIcons/ult_30035</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Rat it go~! 전부 얼어붙어라!</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Rat It Go!</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>#8fd3f4</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>ratitgo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19738,8 +21467,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E330"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -21825,7 +23554,7 @@
       <c r="D95" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -27024,6 +28753,185 @@
           <t>#f2c94c</t>
         </is>
       </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>어둠보다 검고, 치즈보다 고소한 것이여…</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>내 안에 잠든 폭렬의 힘이여, 지금 깨어나라…!</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>익스플로~~~젼!!!</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>#ff6a4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>…하루 한 발. 이제 손가락 하나 못 움직여.</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>30034</v>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>c5</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>털썩</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>찍찍… 손끝이 시려 온다…</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>Rat it go~~!!</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>#8fd3f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>얼음성 완성! 아무도 못 움직여!</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>30035</v>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>…근데 나도 좀 추워.</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E330" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27037,7 +28945,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -27862,7 +29770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -29886,6 +31794,636 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Savory_Smell</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>반경 안 물건이 일정 시간 받는 피해 증가 (고소한 냄새)</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>받는 피해 증가율</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>지속 (초)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Tune_Up</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>부품이 모이면 반경 안 가장 센 동료 공격력 증가 (부품 수 = 패시브 Part_Collect 밸류_02)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>공격력 증가율</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>지속 (초)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Blaster_Shot</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>가까운 물건에 블래스터 여러 발 (명중률 = 패시브 Aim_Assist), 다 맞으면 추가 피해</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>발 수</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>발당 피해 계수</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>모두 맞음 추가 피해율</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>대상 탐색 반경</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>탄 속도</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Self_Destruct</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>심지가 다 타면 가장 가까운 막힌 벽으로 돌진해 폭발 후 사라짐 (쳇바퀴 훈련 없이 바로)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>벽 피해 계수</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>폭발 반경</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>물건 피해 계수</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Patty_Slam</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>패티가 꽉 차면 부딪힐 때 물건으로 뛰어올라 내려찍음, 패티 초기화</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>직격 피해 계수</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>반경 피해 계수</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>대상 탐색 반경</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Power</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>필살기 위력 증가, 쓰고 나면 반동 기절</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>필살기 위력 배율</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>반동 기절 (초)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>Grill_Stack</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>갉을 때마다 공격력 증가 (쌓임), 안 갉으면 식음</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>한 번당 공격력 증가율</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>최대 쌓임</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>식기까지 (초)</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Part_Collect</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>물건을 부술 때마다 부품 (액션 Tune_Up 재료)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>한 번당 부품</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>필요(최대) 부품</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>Aim_Assist</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>블래스터 명중률, 빗나갈 때마다 증가 (맞으면 초기화)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>기본 명중률</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>빗나갈 때 증가</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Burning_Fuse</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>심지(꼬리)가 타들어감, 다 타면 자폭 액션</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>심지 시간 (초)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>Patty_Stack</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>물건을 부술 때마다 패티 (몸 두께·공격력 증가)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>최대 패티</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>장당 두께 증가</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>장당 공격력 증가율</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>Ice_Missile</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>고드름 미사일을 만들어 대상에게 유도 (맞으면 피해 + 빙결 스택)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>미사일 수</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>발당 피해 계수</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>찾는 반경</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>미사일 속도</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>Data_Boost</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>주변 쥐 공격력 강화 버프 (데이터 전송)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>공격력 + 비율</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>반경</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>지속 (초)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>Frost_Stack</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>생명체를 때릴 때마다 빙결 스택: 스택만큼 느려짐, 최대면 꽁꽁</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>스택당 느려짐</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>최대 스택</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>꽁꽁 시간 (초)</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>스택 유지 시간 (초)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>Rush_Range_Up</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>쥐 집결(클릭 총공격) 범위 증가 (여러 마리여도 한 번)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>범위 + (화면 크기 비율)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -35405,4 +35407,1079 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>초필살기 id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>쥐 code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>초필살기 이름</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>초필살기 이름 키</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>본 연출 자막</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>본 연출 자막 키</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>피니시 자막</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>피니시 자막 키</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>연출 방식</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>기획 (한 동작 → 피니시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>super_id</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>code_id</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>super_name</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>super_name_sk</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>super_line</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>super_line_sk</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>finish_line</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>finish_line_sk</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>31001</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>zapham</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>도시 대정전</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4231001</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>찌릿… 도시 전체를 충전 중!</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4331001</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>번개가 하늘을 가른다!!</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>4431001</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Blackout_Bolt</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>불이 꺼짐 → 번개가 화면을 가름</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>31002</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>parkrat</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>쥐랜드 불꽃 퍼레이드</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>4231002</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>퍼레이드 수레 출발~!</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4331002</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>피날레 폭죽 발사!!</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>4431002</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>퍼레이드 수레 → 폭죽</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>31003</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>emperor</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>천하통일 대관식</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>4231003</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>짐의 대관식이니라!</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4331003</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>온 하늘에 축포를 올려라!!</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>4431003</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>왕관 → 하늘 가득 폭죽</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>31004</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>pharaoh</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>태양신의 심판</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>4231004</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>태양 원반이 떠오른다…</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4331004</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>모든 것이 하얗게 타오른다!!</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>4431004</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>태양 원반 → 화면이 하얗게 탐</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>31005</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>knight</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>원탁의 기사단</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>4231005</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>원탁의 기사들이여, 돌격!</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4331005</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>성검 일격!!</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>4431005</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>유령 기사 돌진 → 검 일격</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>31006</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>sultan</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>소원 세 개</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4231006</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>첫째 소원, 둘째 소원…</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4331006</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>마지막 소원! 전부 날려 줘!!</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>4431006</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>소원 1·2 → 소원 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>31007</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>alien</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>모선 강림</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>4231007</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>하늘이… 그림자로 덮인다</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4331007</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>모선 주포 발사!!</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>4431007</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>모선 그림자 → 광선</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>31008</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>streamrat</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>구독자 100만 기념 방송</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4231008</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>채팅창 폭주! 후원 폭주!</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4331008</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>구독자 100만 달성!!</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>4431008</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>채팅·후원 폭주 → "100만!"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>31009</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ramjui</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>람쥐썬더 최종장</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>4231009</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>도토리 천둥이 쏟아진다!</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4331009</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>람쥐썬더!!</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>4431009</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>도토리 천둥 → 거대 낙뢰</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>31010</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>jwerry</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>줴리 감사합니다 (앵콜)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4231010</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>커튼이 오른다… 앵콜!</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4331010</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>줴리 감사합니다!!</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>4431010</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>커튼 → 관객석 쥐들 인사</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>31011</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>starchef</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3스타 풀코스</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4231011</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>전채, 수프… 다음은?</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>4331011</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>메인 디시 나왔습니다!!</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4431011</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>접시 두 개 → 메인 디시</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>31012</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>jjdetective</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>사건 종결</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4231012</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>범인은… 바로 너다!</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>4331012</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>사건 종결!!</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>4431012</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>돋보기로 범인 확대 → 슛</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>31013</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>fondue</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>치즈 대홍수</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4231013</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>치즈가 차오른다…!</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>4331013</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>치즈 대홍수!!</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>4431013</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>치즈가 차오름 → 파도</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>31014</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>bomber</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>익스플로전 · 극</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4231014</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>마법진 전개… 겹겹이!</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>4331014</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>익스플로전!!!</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>4431014</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>마법진 겹겹이 → 화면 전체 폭발</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>31015</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>icequeen</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>영원한 겨울</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>4231015</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>세상이 얼어붙는다…</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>4331015</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>산산조각!!</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>4431015</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>화면이 얼어 금 감 → 깨짐</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>키</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>unlock_level</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>쳇바퀴 훈련 이 레벨 이상 (신화만)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>stack_need</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>자기 필살기를 끝까지 쓴 횟수 (판 동안, 종마다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hit_count</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>본 연출 다단 히트 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hit_mul</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>다단 한 타 = 공격력(스킬 피해) × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>finish_mul</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>피니시 = 공격력 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>boss_cap</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>보스는 초필살기 한 번에 최대 체력의 이 비율까지만</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>t_enter</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>① 진입 끝 (초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>t_cutin</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>② 컷인 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>t_act</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>③ 본 연출 끝 = 피니시 순간</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>t_finish</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>④ 피니시 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>t_end</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>⑤ 걷힘 끝 = 전체 길이</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Character" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -36227,7 +36227,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>산산조각!!</t>
+          <t>전부 꽁꽁!!</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
@@ -36240,7 +36240,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>화면이 얼어 금 감 → 깨짐</t>
+          <t>얼음성 낙하 → 하늘에서 우박 섞인 눈보라 광역 (컷신 뒤 게임 화면, 화면 안 생명체 꽁꽁)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
@@ -5651,6 +5651,63 @@
       </c>
       <c r="O90" s="2" t="n"/>
     </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>10088</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>메이드 쥐</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>1010088</v>
+      </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>maid</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>Mythic</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>Rat</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>472</v>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>20088</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>21088</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>30036</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>커다란 회중시계를 늘 차고 다니는 완벽한 메이드 쥐. 청소도 서빙도 눈 깜짝할 새 끝낸다. 비결을 물으면 "시간은 충분했거든요." 하고 웃는다.</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1110088</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Parts/maid</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5662,7 +5719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W176"/>
+  <dimension ref="A1:W178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21084,6 +21141,180 @@
         <v>1321087</v>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>20088</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>완벽한 뒷정리</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>1220088</v>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="E177" s="1" t="inlineStr">
+        <is>
+          <t>Destroy_Item</t>
+        </is>
+      </c>
+      <c r="F177" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" s="1" t="inlineStr">
+        <is>
+          <t>Cheese_Boost</t>
+        </is>
+      </c>
+      <c r="L177" s="1" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" s="1" t="inlineStr">
+        <is>
+          <t>🧹</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20088</t>
+        </is>
+      </c>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>이 쥐가 부순 물건 치즈 ×1.4</t>
+        </is>
+      </c>
+      <c r="W177" s="2" t="n">
+        <v>1320006</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>21088</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>티 타임</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>1221088</v>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="F178" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="G178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" s="1" t="inlineStr">
+        <is>
+          <t>Cheer</t>
+        </is>
+      </c>
+      <c r="L178" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M178" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="N178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S178" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="T178" s="1" t="inlineStr">
+        <is>
+          <t>☕</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21088</t>
+        </is>
+      </c>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>20초마다 → 티 타임: 주변 동료 전원 광란 6.0초 (속도·피해 ×1.5)</t>
+        </is>
+      </c>
+      <c r="W178" s="2" t="n">
+        <v>1321088</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21095,7 +21326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23439,6 +23670,68 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>살인 인형</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1430036</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>UltTimeStop</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>회중시계로 시간 정지(화면 회색 · 연출만) → 화면 안 물건·생명체 둘레 공중에 칼을 잔뜩 깔아 둠 → 시간이 다시 흐르면 칼이 일제히 꽂힘</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1530036</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>NewRats/maid_knife, NewRats/maid_clock</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>UltIcons/ult_30036</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>시간이여, 멈춰라!</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1630036</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>그리고 시간은 움직인다</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>#d8b45a</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>timestop</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23450,7 +23743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -31912,6 +32205,124 @@
         <v>30</v>
       </c>
       <c r="F330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>c1</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>째깍… 째깍…</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="n">
+        <v>1700321</v>
+      </c>
+      <c r="E331" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>c2</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>시간이여, 멈춰라!</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="n">
+        <v>1700322</v>
+      </c>
+      <c r="E332" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>#f1dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>c3</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>…그리고 시간은 움직인다.</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>1700323</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>#ffffff</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>c4</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>청소 끝났습니다.</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="n">
+        <v>1700324</v>
+      </c>
+      <c r="E334" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>30036</v>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>c5</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>(칼은 이따 제가 다 주울게요)</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>1700325</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F335" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35415,7 +35826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36241,6 +36652,50 @@
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>얼음성 낙하 → 하늘에서 우박 섞인 눈보라 광역 (컷신 뒤 게임 화면, 화면 안 생명체 꽁꽁)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>31016</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>maid</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>메이드의 세계</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>4231016</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>시간… 정지.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>4331016</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>칼날의 비!!</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>4431016</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>회중시계 째깍 → 세상이 회색으로 멈춤 → 하늘을 덮는 칼의 벽 → 손가락 딱, 시간 재개 → 게임 화면 칼 비</t>
         </is>
       </c>
     </row>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
@@ -5651,63 +5651,6 @@
       </c>
       <c r="O90" s="2" t="n"/>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>10088</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>메이드 쥐</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>1010088</v>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>maid</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>Mythic</t>
-        </is>
-      </c>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>Rat</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>472</v>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>20088</v>
-      </c>
-      <c r="I91" s="1" t="n">
-        <v>21088</v>
-      </c>
-      <c r="J91" s="1" t="n">
-        <v>30036</v>
-      </c>
-      <c r="K91" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>커다란 회중시계를 늘 차고 다니는 완벽한 메이드 쥐. 청소도 서빙도 눈 깜짝할 새 끝낸다. 비결을 물으면 "시간은 충분했거든요." 하고 웃는다.</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>1110088</v>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>Parts/maid</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5719,7 +5662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W178"/>
+  <dimension ref="A1:W176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21141,180 +21084,6 @@
         <v>1321087</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="1" t="n">
-        <v>20088</v>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>완벽한 뒷정리</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>1220088</v>
-      </c>
-      <c r="D177" s="1" t="inlineStr">
-        <is>
-          <t>Passive</t>
-        </is>
-      </c>
-      <c r="E177" s="1" t="inlineStr">
-        <is>
-          <t>Destroy_Item</t>
-        </is>
-      </c>
-      <c r="F177" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K177" s="1" t="inlineStr">
-        <is>
-          <t>Cheese_Boost</t>
-        </is>
-      </c>
-      <c r="L177" s="1" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S177" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" s="1" t="inlineStr">
-        <is>
-          <t>🧹</t>
-        </is>
-      </c>
-      <c r="U177" s="2" t="inlineStr">
-        <is>
-          <t>RatSkillIcons/rs_20088</t>
-        </is>
-      </c>
-      <c r="V177" s="2" t="inlineStr">
-        <is>
-          <t>이 쥐가 부순 물건 치즈 ×1.4</t>
-        </is>
-      </c>
-      <c r="W177" s="2" t="n">
-        <v>1320006</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="1" t="n">
-        <v>21088</v>
-      </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>티 타임</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>1221088</v>
-      </c>
-      <c r="D178" s="1" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="E178" s="1" t="inlineStr">
-        <is>
-          <t>Interval</t>
-        </is>
-      </c>
-      <c r="F178" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="G178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="1" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="I178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>Cheer</t>
-        </is>
-      </c>
-      <c r="L178" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="M178" s="1" t="n">
-        <v>320</v>
-      </c>
-      <c r="N178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q178" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R178" s="1" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S178" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="T178" s="1" t="inlineStr">
-        <is>
-          <t>☕</t>
-        </is>
-      </c>
-      <c r="U178" s="2" t="inlineStr">
-        <is>
-          <t>RatSkillIcons/rs_21088</t>
-        </is>
-      </c>
-      <c r="V178" s="2" t="inlineStr">
-        <is>
-          <t>20초마다 → 티 타임: 주변 동료 전원 광란 6.0초 (속도·피해 ×1.5)</t>
-        </is>
-      </c>
-      <c r="W178" s="2" t="n">
-        <v>1321088</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21326,7 +21095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23670,68 +23439,6 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>살인 인형</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>1430036</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>UltTimeStop</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>회중시계로 시간 정지(화면 회색 · 연출만) → 화면 안 물건·생명체 둘레 공중에 칼을 잔뜩 깔아 둠 → 시간이 다시 흐르면 칼이 일제히 꽂힘</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1530036</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>NewRats/maid_knife, NewRats/maid_clock</t>
-        </is>
-      </c>
-      <c r="H39" s="1" t="n">
-        <v>240</v>
-      </c>
-      <c r="I39" s="1" t="inlineStr">
-        <is>
-          <t>UltIcons/ult_30036</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>시간이여, 멈춰라!</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="n">
-        <v>1630036</v>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>그리고 시간은 움직인다</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>#d8b45a</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>timestop</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23743,7 +23450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F335"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32205,124 +31912,6 @@
         <v>30</v>
       </c>
       <c r="F330" s="2" t="n"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="2" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B331" s="2" t="inlineStr">
-        <is>
-          <t>c1</t>
-        </is>
-      </c>
-      <c r="C331" s="2" t="inlineStr">
-        <is>
-          <t>째깍… 째깍…</t>
-        </is>
-      </c>
-      <c r="D331" s="2" t="n">
-        <v>1700321</v>
-      </c>
-      <c r="E331" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F331" s="2" t="n"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="2" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B332" s="2" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="C332" s="2" t="inlineStr">
-        <is>
-          <t>시간이여, 멈춰라!</t>
-        </is>
-      </c>
-      <c r="D332" s="2" t="n">
-        <v>1700322</v>
-      </c>
-      <c r="E332" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="F332" s="2" t="inlineStr">
-        <is>
-          <t>#f1dfa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="2" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B333" s="2" t="inlineStr">
-        <is>
-          <t>c3</t>
-        </is>
-      </c>
-      <c r="C333" s="2" t="inlineStr">
-        <is>
-          <t>…그리고 시간은 움직인다.</t>
-        </is>
-      </c>
-      <c r="D333" s="2" t="n">
-        <v>1700323</v>
-      </c>
-      <c r="E333" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F333" s="2" t="inlineStr">
-        <is>
-          <t>#ffffff</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="2" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B334" s="2" t="inlineStr">
-        <is>
-          <t>c4</t>
-        </is>
-      </c>
-      <c r="C334" s="2" t="inlineStr">
-        <is>
-          <t>청소 끝났습니다.</t>
-        </is>
-      </c>
-      <c r="D334" s="2" t="n">
-        <v>1700324</v>
-      </c>
-      <c r="E334" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F334" s="2" t="n"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="2" t="n">
-        <v>30036</v>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>c5</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="inlineStr">
-        <is>
-          <t>(칼은 이따 제가 다 주울게요)</t>
-        </is>
-      </c>
-      <c r="D335" s="2" t="n">
-        <v>1700325</v>
-      </c>
-      <c r="E335" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F335" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35826,7 +35415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36652,50 +36241,6 @@
       <c r="J18" s="2" t="inlineStr">
         <is>
           <t>얼음성 낙하 → 하늘에서 우박 섞인 눈보라 광역 (컷신 뒤 게임 화면, 화면 안 생명체 꽁꽁)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>31016</v>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>maid</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>메이드의 세계</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>4231016</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>시간… 정지.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>4331016</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>칼날의 비!!</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>4431016</v>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>회중시계 째깍 → 세상이 회색으로 멈춤 → 하늘을 덮는 칼의 벽 → 손가락 딱, 시간 재개 → 게임 화면 칼 비</t>
         </is>
       </c>
     </row>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O90"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="11.75" customWidth="1" min="1" max="1"/>
@@ -5651,6 +5651,118 @@
       </c>
       <c r="O90" s="2" t="n"/>
     </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>10088</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>콩쥐팥쥐</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1010088</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>kongpat</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>52</v>
+      </c>
+      <c r="H91" t="n">
+        <v>20088</v>
+      </c>
+      <c r="I91" t="n">
+        <v>21088</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>8</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>등을 맞대고 붙어 버린 한복 쌍둥이. 위에 붙은 한 마리는 늘 거꾸로 버둥거리고, 뛰어오르면 공중제비로 위아래가 바뀐다.</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>1110088</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Parts/kongpat</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>10089</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>나비쥐</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1010089</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>butterfly</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mouse</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" t="n">
+        <v>20089</v>
+      </c>
+      <c r="I92" t="n">
+        <v>21089</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>8</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>커다란 귀를 날개처럼 팔랑이며 땅에서 살짝 떠서 다닌다. 날갯짓 한 번이 나비 효과가 된다.</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>1110089</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Parts/butterfly</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5662,7 +5774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W176"/>
+  <dimension ref="A1:W180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21082,6 +21194,354 @@
       </c>
       <c r="W176" s="2" t="n">
         <v>1321087</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>20088</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>둘이서 두 번</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1220088</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Hit_Item</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Double_Bite</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="n">
+        <v>0</v>
+      </c>
+      <c r="S177" t="n">
+        <v>0</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>👯</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20088</t>
+        </is>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>한 번 더 갉을 확률 30% (둘이서 한입씩)</t>
+        </is>
+      </c>
+      <c r="W177" t="n">
+        <v>1320088</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>21088</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>공중제비 쌍둥이</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1221088</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Hit_Item</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Jump_Slam</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N178" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S178" t="n">
+        <v>6</v>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>🤸</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21088</t>
+        </is>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>물건에 부딪힐 때 4% 확률로 → 공중제비 쌍둥이: 3번 뛰어올라 공중제비로 위아래를 바꾸며 쾅! 내려찍기 (반경 100)</t>
+        </is>
+      </c>
+      <c r="W178" t="n">
+        <v>1321088</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>20089</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>나비 효과</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1220089</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Hit_Item</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Crit_Boost</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0</v>
+      </c>
+      <c r="S179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>🦋</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_20089</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>크리티컬 확률 +10%, 크리티컬 ×3.7</t>
+        </is>
+      </c>
+      <c r="W179" t="n">
+        <v>1320089</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>21089</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>비늘가루 소나기</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1221089</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>10</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Savory_Smell</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M180" t="n">
+        <v>300</v>
+      </c>
+      <c r="N180" t="n">
+        <v>5</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S180" t="n">
+        <v>6</v>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>✨</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>RatSkillIcons/rs_21089</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>10초마다 → 비늘가루 소나기: 반경 300 안 물건이 5초 동안 받는 피해 +30%</t>
+        </is>
+      </c>
+      <c r="W180" t="n">
+        <v>1321089</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -5670,7 +5670,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="H91" t="n">
         <v>20088</v>

--- a/Data_Table/쥐 캐릭터 테이블.xlsx
+++ b/Data_Table/쥐 캐릭터 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Character" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Skill" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Character" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skill" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ultimate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Caption" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ult_Charge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Effect_Type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Ult" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Super_Config" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>어디선가 본 것 같은 요리사. 치즈 요리만 18가지.</t>
+          <t>치즈 요리만 18가지를 아는 요리사 쥐.</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>하수구에서 무술을 배웠다. 피자를 좋아한다.</t>
+          <t>하수구에서 무술을 배웠다. 수리검 대신 해바라기씨를 던진다.</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>전기 쥐 코스프레 중인 햄스터. 사실 전기는 등에 멘 건전지에서 나온다.</t>
+          <t>번개 머리띠를 쓰고 전기 흉내를 내는 햄스터. 사실 전기는 등에 멘 건전지에서 나온다.</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>놀이공원 기념품 가게에서 산 동그란 귀 머리띠를 절대 안 벗는다. 자기가 원조라고 우긴다.</t>
+          <t>놀이공원 기념품 가게에서 산 머리띠를 절대 안 벗는다. 퍼레이드만 보이면 맨 앞에 선다.</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>폭발 마법(이라고 우기는 폭탄)만 배웠다. 하루에 딱 한 발 쏘고 그대로 뻗는다. 안대는 멋으로 찼다.</t>
+          <t>폭탄을 마법이라고 우기는 쥐. 한 번 크게 터뜨리고 나면 기운이 쭉 빠져 뻗는다.</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>엘사가 연상되는 얼음 마법사 쥐. 때릴 때마다 생명체를 얼린다. 렛잇고를 부르면 동료 쥐들도 덜덜 떤다.</t>
+          <t>얼음 마법을 쓰는 쥐 여왕. 때릴 때마다 생명체를 얼린다. 노래를 부르면 동료 쥐들도 덜덜 떤다.</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>그림자 분신술</t>
+          <t>그림자 쥐떼</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>물건에 부딪힐 때 3% 확률로 → 그림자 분신술: 동료 3마리 소환 (6초 동안 함께 난동)</t>
+          <t>물건에 부딪힐 때 3% 확률로 → 그림자 쥐떼: 동료 3마리 소환 (6초 동안 함께 난동)</t>
         </is>
       </c>
       <c r="W75" s="2" t="n">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>건전지 백만 볼트</t>
+          <t>건전지 대방전</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>18초마다 → 건전지 백만 볼트: 360° 회전 레이저 (피해 ×8.0)</t>
+          <t>18초마다 → 건전지 대방전: 360° 회전 레이저 (피해 ×8.0)</t>
         </is>
       </c>
       <c r="W137" s="2" t="n">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>폭렬 외길</t>
+          <t>폭탄 외길</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>천본앵 난무</t>
+          <t>벚꽃 일섬</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>백만 볼트…! (건전지는 1.5볼트)</t>
+          <t>충전 완료…! (건전지는 1.5볼트)</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -23815,7 +23815,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>내 이름은 찍구밍! 최강의 폭렬 마법을 다루는 쥐!</t>
+          <t>이 한 방에 전부 건다! 폭탄 마법, 발사!</t>
         </is>
       </c>
       <c r="K37" s="2" t="n">
@@ -25230,7 +25230,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>뇌의 호흡…</t>
+          <t>번개의 기운…</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>제1형…</t>
+          <t>첫 번째 칼…</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>벽력일섬!!</t>
+          <t>번개 일섬!!</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
